--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -4934,7 +4934,50 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="15.75" customHeight="1" s="18"/>
+    <row r="113" ht="15.75" customHeight="1" s="18">
+      <c r="A113" s="21" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>プールバッグがフリンジ仕様に！？長女の「糸を引っ張ったらこうなっちゃった」</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="inlineStr">
+        <is>
+          <t>2028/06/05</t>
+        </is>
+      </c>
+      <c r="E113" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">プールバッグがフリンジ仕様に！？😂
+「お母さん、このバッグすごいことになっちゃって…」
+見ると肩ベルトがフリンジのように糸状に。
+犯人は「糸を引っ張ったらこうなっちゃった」と語る長女本人でした😂
+セロテープを謎に三角形に折る、剥がしちゃいけないシートを無意識に剥がす…
+数々の前科に、糸があったらそりゃ引っ張るわと納得。
+次のバッグは糸が出ないタイプにします！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="114" ht="15.75" customHeight="1" s="18"/>
     <row r="115" ht="15.75" customHeight="1" s="18"/>
     <row r="116" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -4978,7 +4978,50 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="15.75" customHeight="1" s="18"/>
+    <row r="114" ht="15.75" customHeight="1" s="18">
+      <c r="A114" s="23" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>朝から勃発「メッシvsロナウド論争」。三者三様すぎて誰も噛み合っていない件</t>
+        </is>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="inlineStr">
+        <is>
+          <t>2028/06/12</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朝から勃発「メッシvsロナウド論争」⚽😂
+ワールドカップで白熱する我が家。
+「お前はアルゼンチンだからメッシだな！」と決めつける長男、
+「どっちもはダメ！」と二択を強要する長女、
+「俺どっちも好き！」なのに論争に入れてもらえない次男😂
+三者三様すぎて誰も噛み合っていません。
+ところで登校まであと5分。身支度は…？
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="115" ht="15.75" customHeight="1" s="18"/>
     <row r="116" ht="15.75" customHeight="1" s="18"/>
     <row r="117" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5022,7 +5022,49 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="15.75" customHeight="1" s="18"/>
+    <row r="115" ht="15.75" customHeight="1" s="18">
+      <c r="A115" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="21" t="inlineStr">
+        <is>
+          <t>小学生のプールバッグの選び方。学校用とスイミング用で使い分けたら大正解だった話</t>
+        </is>
+      </c>
+      <c r="C115" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="inlineStr">
+        <is>
+          <t>2028/06/19</t>
+        </is>
+      </c>
+      <c r="E115" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小学生のプールバッグ、学校用とスイミング用で使い分けたら大正解でした🏊
+フリンジ事件からの買い替え。
+学校用は透明PVCの手提げ→忘れ物チェックがラク！
+スイミング用は黒の巾着リュック→ポイポイ入れてギュッと縛るだけ！
+小4女子はもうピンクよりシックな色がお好み。
+どちらも1,000円以下で無事フリンジバッグから卒業です✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="116" ht="15.75" customHeight="1" s="18"/>
     <row r="117" ht="15.75" customHeight="1" s="18"/>
     <row r="118" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5065,7 +5065,51 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="15.75" customHeight="1" s="18"/>
+    <row r="116" ht="15.75" customHeight="1" s="18">
+      <c r="A116" s="23" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="23" t="inlineStr">
+        <is>
+          <t>小1の「遊ぶ約束」は当てにならない。すれ違い続きの公園待ち合わせ</t>
+        </is>
+      </c>
+      <c r="C116" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/09</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="inlineStr">
+        <is>
+          <t>2028/06/26</t>
+        </is>
+      </c>
+      <c r="E116" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小1の「遊ぶ約束」は当てにならない😂
+「〇〇くんと公園で15時に約束した！」という次男。
+一緒に公園へ行くも、15分待っても30分待っても友達は現れず…
+諦めて帰ろうとしたその時、友達がお母さんと登場！
+実は「バス停で待ち合わせ」と「公園で待ち合わせ」で
+お互いの認識が全く違っていました😂
+母たちが詫び合う横で、二人はもう遊び始めてる。
+小1の約束にはまだ見守りが必要です！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="117" ht="15.75" customHeight="1" s="18"/>
     <row r="118" ht="15.75" customHeight="1" s="18"/>
     <row r="119" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5110,7 +5110,50 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="15.75" customHeight="1" s="18"/>
+    <row r="117" ht="15.75" customHeight="1" s="18">
+      <c r="A117" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>次男の「そうだよ」問題。知ったかぶりの裏に隠れていた意外なスイッチ</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="inlineStr">
+        <is>
+          <t>2028/07/03</t>
+        </is>
+      </c>
+      <c r="E117" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">次男の「そうだよ」問題😂
+知らないことも「そうだよ！」と自信満々の次男。
+今朝も「ほのめかす」の説明に、絶対知らないのに「そうだよー！」と便乗😂
+「知らないことは恥ずかしくない」と説教する兄姉、立派。
+でもその知ったかぶり、実は小さい頃に大人が笑って喜んだ
+「成功体験スイッチ」だったのかも。
+しばらく続きそうな「そうだよ」、これからは理由を聞いてみます。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="118" ht="15.75" customHeight="1" s="18"/>
     <row r="119" ht="15.75" customHeight="1" s="18"/>
     <row r="120" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5154,7 +5154,51 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="15.75" customHeight="1" s="18"/>
+    <row r="118" ht="15.75" customHeight="1" s="18">
+      <c r="A118" s="23" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>子どものロブロックスが突然BAN！身に覚えがない時に親が確認すべきことと、やってはいけないこと</t>
+        </is>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/11</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="inlineStr">
+        <is>
+          <t>2028/07/10</t>
+        </is>
+      </c>
+      <c r="E118" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子どものロブロックスが突然BAN😱
+「チートなんて使ってない！」と泣く長男。
+身に覚えがなくてもBANされることがあるんです。
+我が家の盲点は「知らない人からもらったアイテム」。
+そして一番危険なのは、パニック中に検索して出てくる
+「復旧してあげる」という詐欺の甘い言葉…。
+親子でやった振り返りチェックリスト、
+異議申し立ての注意点まで実体験でまとめました。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="119" ht="15.75" customHeight="1" s="18"/>
     <row r="120" ht="15.75" customHeight="1" s="18"/>
     <row r="121" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5199,7 +5199,51 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="15.75" customHeight="1" s="18"/>
+    <row r="119" ht="15.75" customHeight="1" s="18">
+      <c r="A119" s="21" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>「どちら様ですか？」新しい服を着ただけで別人扱いされた長男の、完璧な返し</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/11</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="inlineStr">
+        <is>
+          <t>2028/07/17</t>
+        </is>
+      </c>
+      <c r="E119" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新しい服を着ただけで「どちら様ですか？」😂
+お気に入り2セットを1年以上着回す長男に、
+新しい短パン＆Tシャツをコーディネート。
+いつもと違う服で登校したら、仲良しの友達から
+「どちら様ですか？」と言われたそうで…
+長男の返しは「名乗るほどの者ではありません」😂
+小6男子のセンス、侮れません。
+スタメン服、ようやく3セットになりました！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="120" ht="15.75" customHeight="1" s="18"/>
     <row r="121" ht="15.75" customHeight="1" s="18"/>
     <row r="122" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5244,7 +5244,50 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="15.75" customHeight="1" s="18"/>
+    <row r="120" ht="15.75" customHeight="1" s="18">
+      <c r="A120" s="23" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>同じ服しか着ない小学生男子。新しい服を受け入れてもらえた「選び方のコツ」</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/12</t>
+        </is>
+      </c>
+      <c r="D120" s="22" t="inlineStr">
+        <is>
+          <t>2028/07/24</t>
+        </is>
+      </c>
+      <c r="E120" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同じ服しか着ない小学生男子、いませんか？👕
+お気に入り2セットを1年以上着回す我が家の長男。
+でも観察してみたら、頑固なんじゃなくて
+「楽・サラサラ・合わせやすい」という明確な基準がありました。
+その基準に合わせて選んだセール800円の短パンは、
+無事スタメン入り✨
+こだわり男子への新戦力投入、3つのコツをまとめました。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="121" ht="15.75" customHeight="1" s="18"/>
     <row r="122" ht="15.75" customHeight="1" s="18"/>
     <row r="123" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5288,7 +5288,51 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="15.75" customHeight="1" s="18"/>
+    <row r="121" ht="15.75" customHeight="1" s="18">
+      <c r="A121" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>「肩幅広し、足細し、堀ふかし、頭小さし」長男のベリンガム評がもはやラップ</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/12</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="inlineStr">
+        <is>
+          <t>2028/07/31</t>
+        </is>
+      </c>
+      <c r="E121" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">長男のベリンガム評がもはやラップ🎤
+「ベリンガムかっこいいね」と家族で盛り上がっていたら、
+長男から飛び出した称賛の言葉——
+「肩幅広し、足細し、堀ふかし、頭小さし。」
+しかもこれ、かつて我が家に君臨した伝説のおもちゃ
+「肩幅ひろし」のサンプリング😂
+韻を踏んで語彙を重ねていく子どもの思考、
+まるでラッパーです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="122" ht="15.75" customHeight="1" s="18"/>
     <row r="123" ht="15.75" customHeight="1" s="18"/>
     <row r="124" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5333,7 +5333,51 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="15.75" customHeight="1" s="18"/>
+    <row r="122" ht="15.75" customHeight="1" s="18">
+      <c r="A122" s="23" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="23" t="inlineStr">
+        <is>
+          <t>小6長男、念願のスマホデビュー。親子で決めた「スマホの約束」6つ</t>
+        </is>
+      </c>
+      <c r="C122" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/12</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="inlineStr">
+        <is>
+          <t>2028/08/07</t>
+        </is>
+      </c>
+      <c r="E122" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小6長男、ついにスマホデビュー📱✨
+七夕の短冊に「携帯が欲しい」と書いていた長男。
+テスト勉強や忘れ物確認、彼なりの努力を見て
+夏休み前に渡すことを決めました。
+でも、ただでは渡しません😊
+ルールは親が決めるのではなく、親子で一緒に考えて6つの約束に。
+LINEで送って「見返せる形」にするのがポイントです。
+ルールは決めて終わりじゃなく、ここからが本番！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="123" ht="15.75" customHeight="1" s="18"/>
     <row r="124" ht="15.75" customHeight="1" s="18"/>
     <row r="125" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5378,7 +5378,51 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="15.75" customHeight="1" s="18"/>
+    <row r="123" ht="15.75" customHeight="1" s="18">
+      <c r="A123" s="21" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>小学生のスマホデビュー、我が家は「お下がりiPhone＋格安SIM 1GB」にした理由</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/12</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="inlineStr">
+        <is>
+          <t>2028/08/14</t>
+        </is>
+      </c>
+      <c r="E123" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小学生のスマホデビュー、いくらかける？📱
+我が家の答えは「お下がりiPhone＋格安SIM 1GB」。
+新たに買ったものはゼロです✨
+・Wi-Fi中心の生活なら1GBで十分
+・通話もメールもLINEに集約して見守りやすく
+・ギガ超過分は本人のお小遣いから！
+お金とギガの管理も練習できる、
+ミニマムスタートのすすめです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="124" ht="15.75" customHeight="1" s="18"/>
     <row r="125" ht="15.75" customHeight="1" s="18"/>
     <row r="126" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5423,7 +5423,50 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="15.75" customHeight="1" s="18"/>
+    <row r="124" ht="15.75" customHeight="1" s="18">
+      <c r="A124" s="23" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>「パパ、これ脂質がちょっと多いけど食べる？」次男、母の言葉をそのまま営業に使う</t>
+        </is>
+      </c>
+      <c r="C124" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="inlineStr">
+        <is>
+          <t>2028/08/21</t>
+        </is>
+      </c>
+      <c r="E124" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「パパ、これ脂質がちょっと多いけど食べる？」😂
+ケースに残った芋けんぴ2つ。
+「お母さんは脂質が多いから食べないよ」と答えた直後——
+次男がパパのところへ行き
+「脂質がちょっと多いけど食べる？」と営業開始😂
+脂質が何かも知らないのに、使い方だけ完璧にコピー。
+親の会話、本当によく聞かれています…！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="125" ht="15.75" customHeight="1" s="18"/>
     <row r="126" ht="15.75" customHeight="1" s="18"/>
     <row r="127" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5467,7 +5467,51 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="15.75" customHeight="1" s="18"/>
+    <row r="125" ht="15.75" customHeight="1" s="18">
+      <c r="A125" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="21" t="inlineStr">
+        <is>
+          <t>グリル野菜×塩沼にハマった話。我が家の塩、気づけば8種類になっていました</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="inlineStr">
+        <is>
+          <t>2028/08/28</t>
+        </is>
+      </c>
+      <c r="E125" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">グリル野菜×塩沼にハマりました🧂
+年明けにグリルパン対応のコンロに変えたら、
+野菜を放置で焼くだけのご馳走「グリル野菜」に感動…！
+じゃがいも、玉ねぎ、蓮根、かぼちゃ…なんでも甘くなる✨
+「塩を変えたらもっと美味しいのでは？」と探究心に火がつき、
+気づけば我が家の塩は8種類に😂
+じゃがいも×トリュフ塩は、あのポテチの味になります。
+お気に入りの塩3選はブログで！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="126" ht="15.75" customHeight="1" s="18"/>
     <row r="127" ht="15.75" customHeight="1" s="18"/>
     <row r="128" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5512,7 +5512,52 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="15.75" customHeight="1" s="18"/>
+    <row r="126" ht="15.75" customHeight="1" s="18">
+      <c r="A126" s="23" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="23" t="inlineStr">
+        <is>
+          <t>塩8種類を使い比べてわかった、それぞれの「得意料理」。塩沼住人の正直レビュー</t>
+        </is>
+      </c>
+      <c r="C126" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/18</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="inlineStr">
+        <is>
+          <t>2028/09/04</t>
+        </is>
+      </c>
+      <c r="E126" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塩8種類、使い比べてみた🧂✨
+「そんなに何が違うの？」と言われるけど、
+それぞれに得意料理があるんです！
+・下味の定番→クレイジーソルト(納豆ご飯にも◎)
+・万能選手→ろく助白塩
+・じゃがいも→トリュフ塩(あのポテチの味)
+・ステーキ→ヴェゲタグリルクラシック
+・グリル野菜→のどぐろ塩
+8種類の正直レビュー＋使い分け早見表はブログで！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="127" ht="15.75" customHeight="1" s="18"/>
     <row r="128" ht="15.75" customHeight="1" s="18"/>
     <row r="129" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5558,7 +5558,51 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="15.75" customHeight="1" s="18"/>
+    <row r="127" ht="15.75" customHeight="1" s="18">
+      <c r="A127" s="21" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>5家族22人でBBQお泊まり会。1棟貸し「伊豆クリスタル迎賓館」が大人数に最高だった</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="inlineStr">
+        <is>
+          <t>2028/09/11</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5家族22人でBBQお泊まり会に行ってきました🍻
+今年の宿は1棟貸しの「伊豆クリスタル迎賓館」✨
+テニスコートに24時間掛け流し温泉、カラオケ・麻雀卓まで！
+1棟貸しなら、子どもたちが鬼ごっこしても
+かくれんぼしても誰にも怒られない😂
+BBQはパパたちにお任せして、ママたちは16時にかんぱーい！
+年1回でも「久しぶり」にならない友人たちとの時間、至福でした。
+これでまた1年がんばれます！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="128" ht="15.75" customHeight="1" s="18"/>
     <row r="129" ht="15.75" customHeight="1" s="18"/>
     <row r="130" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5603,7 +5603,51 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="15.75" customHeight="1" s="18"/>
+    <row r="128" ht="15.75" customHeight="1" s="18">
+      <c r="A128" s="23" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="23" t="inlineStr">
+        <is>
+          <t>文具好き小6男子の愛用品レビュー。S20・フリクション・スマッシュ・ロットリング500を本音で語る</t>
+        </is>
+      </c>
+      <c r="C128" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/21</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="inlineStr">
+        <is>
+          <t>2028/09/18</t>
+        </is>
+      </c>
+      <c r="E128" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F128" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文具好き小6男子の愛用品、本音でレビュー✏️
+書き味最高のシャープペン「S20」、
+消せて採点にも便利な「フリクションボール」、
+でも正直に言うと…
+「スマッシュ」はグリップが筆圧に負けて潰れちゃう😂
+「ロットリング500」は芯が折れやすい💦
+良いところも気になるところも、
+子ども目線の本音レビューです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="129" ht="15.75" customHeight="1" s="18"/>
     <row r="130" ht="15.75" customHeight="1" s="18"/>
     <row r="131" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5648,7 +5648,51 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="15.75" customHeight="1" s="18"/>
+    <row r="129" ht="15.75" customHeight="1" s="18">
+      <c r="A129" s="21" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t>「お母さん！すごくない？」宿題は苦手な長男が、ピアノにだけ本気になれる理由</t>
+        </is>
+      </c>
+      <c r="C129" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/21</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="inlineStr">
+        <is>
+          <t>2028/09/25</t>
+        </is>
+      </c>
+      <c r="E129" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「お母さん！すごくない？」😊
+「コウを追いかけて」を弾きたいと言い出してから、
+毎日欠かさずピアノを練習する長男。
+実は目標に向かってコツコツやるのが苦手なタイプなのに、
+なぜここまで頑張れるんだろう…と考えてみたら、
+答えは「毎日の上達を自分で実感できること」。
+小さな成功体験の力ってすごいですね✨
+誇らしそうにキラキラ報告してくれる姿が可愛くて仕方ない毎日です。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="130" ht="15.75" customHeight="1" s="18"/>
     <row r="131" ht="15.75" customHeight="1" s="18"/>
     <row r="132" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5693,7 +5693,52 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15.75" customHeight="1" s="18"/>
+    <row r="130" ht="15.75" customHeight="1" s="18">
+      <c r="A130" s="23" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="23" t="inlineStr">
+        <is>
+          <t>上半身マイケル、下半身は迷子。長女の「アンガールズ感」溢れるダンスが可愛すぎる</t>
+        </is>
+      </c>
+      <c r="C130" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/21</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>2028/10/02</t>
+        </is>
+      </c>
+      <c r="E130" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F130" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上半身マイケル、下半身は迷子😂
+ダンス好きな長女。でもなんか少しダサいんです。
+手足が細長く、首をすくめて踊るので
+アンガールズ感が否めない…
+片手で頭をカッコよく押さえながら
+下手すぎるムーンウォーク、
+ランニングマンもなんかダサい😂
+でも本人は大満足で心のままに踊る姿が可愛くて、
+笑いすぎて母の腹筋が鍛えられています。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="131" ht="15.75" customHeight="1" s="18"/>
     <row r="132" ht="15.75" customHeight="1" s="18"/>
     <row r="133" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5739,7 +5739,53 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="15.75" customHeight="1" s="18"/>
+    <row r="131" ht="15.75" customHeight="1" s="18">
+      <c r="A131" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t>「お母さん、すごくない？」半紙パンパンの書道バッグを見て、長男の整理の概念が崩壊していた話</t>
+        </is>
+      </c>
+      <c r="C131" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/21</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="inlineStr">
+        <is>
+          <t>2028/10/09</t>
+        </is>
+      </c>
+      <c r="E131" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「お母さん、すごくない？」😂
+夏休み初日、道具の整理を頼んだら「忘れていた」長男。
+翌日「やったよ」と言うので見てみると…
+書道バッグがパンパン！中身は使用済みの半紙の山！
+整理＝いらないものを減らす
+整頓＝使いやすくする
+基本から教えてリベンジさせるも、
+「こんな小さいバッグにこんなに入れられてすごくない？」
+……いや、そうじゃない😂
+夏休みはまだ始まったばかりです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="132" ht="15.75" customHeight="1" s="18"/>
     <row r="133" ht="15.75" customHeight="1" s="18"/>
     <row r="134" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5786,7 +5786,51 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="15.75" customHeight="1" s="18"/>
+    <row r="132" ht="15.75" customHeight="1" s="18">
+      <c r="A132" s="21" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="21" t="inlineStr">
+        <is>
+          <t>夏休みの子どもの家事分担、揉めても口出ししなかったら自然に決まった話</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/28</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="inlineStr">
+        <is>
+          <t>2028/10/16</t>
+        </is>
+      </c>
+      <c r="E132" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夏休みの子どもの家事分担、揉めても口出ししなかった話📢
+掃除機・洗濯物・お風呂掃除を3人に任せてみたら、
+最初の数日は毎日揉めまくり…😅
+でも口を出さずに見守っていたら、
+数日で自然に担当が定着！
+「話し合っていない、よくやることが担当になった」と長男。
+それぞれの「楽しい」「褒められる」「楽」の理由で
+自然に住み分けができていました✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="133" ht="15.75" customHeight="1" s="18"/>
     <row r="134" ht="15.75" customHeight="1" s="18"/>
     <row r="135" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5831,7 +5831,52 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="15.75" customHeight="1" s="18"/>
+    <row r="133" ht="15.75" customHeight="1" s="18">
+      <c r="A133" s="23" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="23" t="inlineStr">
+        <is>
+          <t>小6長男が謎かけにハマった朝。「議員とかけてゴキブリ」の心は、まさかの新聞オチ</t>
+        </is>
+      </c>
+      <c r="C133" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="inlineStr">
+        <is>
+          <t>2028/10/23</t>
+        </is>
+      </c>
+      <c r="E133" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小6長男が謎かけにハマった朝😂
+「議員とかけてゴキブリとときます、その心は」
+「どちらも新聞で叩かれるでしょう」
+「スイッチとかけて、シャリとときます」
+「それはどちらも『おす』でしょう」
+朝から長男の謎かけラッシュ、地味に頭を使ってて感心…！
+しかも「ねずっちってすごいよねー」と
+世代を超えて知っていることにもびっくり😳
+SNSってすごいですね。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="15.75" customHeight="1" s="18"/>
     <row r="135" ht="15.75" customHeight="1" s="18"/>
     <row r="136" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5877,7 +5877,50 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="15.75" customHeight="1" s="18"/>
+    <row r="134" ht="15.75" customHeight="1" s="18">
+      <c r="A134" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="21" t="inlineStr">
+        <is>
+          <t>トリュフ醤油、小6男子と夫が食べ比べてわかった「一番合う食べ方」</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="inlineStr">
+        <is>
+          <t>2028/10/30</t>
+        </is>
+      </c>
+      <c r="E134" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F134" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">トリュフ醤油、家族で食べ比べてみました🍄
+長男の感想「めっちゃちゃんとトリュフだし、めっちゃちゃんと醤油」
+「トリュフと醤油が半々だね」的確すぎる表現😂
+夫の感想は「醤油ドレッシングに近いね」
+塩味は控えめで、醤油とオリーブオイルが主役。
+黒トリュフの粒の量で風味が変わるんです✨
+一番合いそうなのはサラダでした！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="135" ht="15.75" customHeight="1" s="18"/>
     <row r="136" ht="15.75" customHeight="1" s="18"/>
     <row r="137" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5921,7 +5921,52 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="15.75" customHeight="1" s="18"/>
+    <row r="135" ht="15.75" customHeight="1" s="18">
+      <c r="A135" s="21" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="21" t="inlineStr">
+        <is>
+          <t>「俺今なら犬の気持ちわかる」14歳おばあちゃん犬との早朝散歩で意思が一致した日</t>
+        </is>
+      </c>
+      <c r="C135" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="inlineStr">
+        <is>
+          <t>2028/11/06</t>
+        </is>
+      </c>
+      <c r="E135" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「俺今なら犬の気持ちわかる」😂
+夫の実家の14歳おばあちゃんパピヨンをお預かり中🐕
+暑くなる前にと5時半に長男と早朝散歩へ。
+あまりにゆっくりな足取りを見て、長男がぽつり。
+「俺今なら犬の気持ちわかる」
+「帰りたい」
+犬と人間の意思がぴったり一致する瞬間、
+初めて見ました😂
+朝から面白い1日の始まりです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="136" ht="15.75" customHeight="1" s="18"/>
     <row r="137" ht="15.75" customHeight="1" s="18"/>
     <row r="138" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -5967,7 +5967,51 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="15.75" customHeight="1" s="18"/>
+    <row r="136" ht="15.75" customHeight="1" s="18">
+      <c r="A136" s="23" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="23" t="inlineStr">
+        <is>
+          <t>犬好きの次男、20分間の行方不明。見つかった先は上階のご近所さんちだった話</t>
+        </is>
+      </c>
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>2028/11/13</t>
+        </is>
+      </c>
+      <c r="E136" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F136" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">犬好きの次男、20分間の行方不明事件😳
+5歳の頃、外出から帰宅した瞬間に次男が消えた我が家。
+大通り沿いということもあり、家族総出で20分間捜索…
+見つけてくれたのは上の階の住人の方。
+そこには、その家の犬と楽しそうに遊ぶ次男の姿が😂
+「知らない犬にテンション上がって居座る」
+まさかのコミュ力に驚いた出来事でした。
+その夜は緊急家族会議です。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="137" ht="15.75" customHeight="1" s="18"/>
     <row r="138" ht="15.75" customHeight="1" s="18"/>
     <row r="139" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6012,7 +6012,51 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="15.75" customHeight="1" s="18"/>
+    <row r="137" ht="15.75" customHeight="1" s="18">
+      <c r="A137" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t>マンション住まいの子どもの迷子対策。20分間の行方不明から決めた「手をつなぐルール」</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="inlineStr">
+        <is>
+          <t>2028/11/20</t>
+        </is>
+      </c>
+      <c r="E137" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マンション住まいの子どもの迷子対策📢
+外出から帰宅した瞬間、5歳の次男が20分間行方不明に。
+原因は「オートロックだから安心」という思い込みでした。
+振り返ってわかったのは、
+大人が荷物整理をしている間の隙間時間。
+家族会議で決めたのは「誰かが必ず手をつなぐ」という
+シンプルなルール。
+同じ悩みの方の参考になれば嬉しいです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="138" ht="15.75" customHeight="1" s="18"/>
     <row r="139" ht="15.75" customHeight="1" s="18"/>
     <row r="140" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6057,7 +6057,52 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="15.75" customHeight="1" s="18"/>
+    <row r="138" ht="15.75" customHeight="1" s="18">
+      <c r="A138" s="23" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>「たねは無限ループだね！」読書感想文は子どもの個性が丸出しになる</t>
+        </is>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>2028/11/27</t>
+        </is>
+      </c>
+      <c r="E138" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F138" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「たねは無限ループだね！」📚
+夏休みの読書感想文、今は任意提出なんです。
+それでも我が家はチャレンジ中！
+小1次男の感想は「たねは無限ループだね！」
+命の循環を一言で言い切る今どきセンス😂
+長女は黒い気持ちを「嫌な気持ち」とオブラートに包む、
+いかにも長女らしい感想…
+手はかかるけど、同じ本を読んで語り合う時間は
+本当に貴重です✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="139" ht="15.75" customHeight="1" s="18"/>
     <row r="140" ht="15.75" customHeight="1" s="18"/>
     <row r="141" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6103,7 +6103,53 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="15.75" customHeight="1" s="18"/>
+    <row r="139" ht="15.75" customHeight="1" s="18">
+      <c r="A139" s="21" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>読書感想文の親サポート。小1と小4で「質問の仕方」をこう変えました</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="inlineStr">
+        <is>
+          <t>2028/12/04</t>
+        </is>
+      </c>
+      <c r="E139" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">読書感想文、「感想は？」と聞いても出てこない…📚
+我が家で実際に使っている質問リストを公開します！
+【小1】五感で具体化
+「どのたねが一番おもしろかった？」
+「形は？色は？さわった感じは？」
+【小4】登場人物→自分→テーマの順
+「主人公はどんな気持ちだったと思う？」
+「自分にも似た経験ある？」
+学年で聞き方を変えるだけで、
+子どもの言葉が自然に出てきます✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="140" ht="15.75" customHeight="1" s="18"/>
     <row r="141" ht="15.75" customHeight="1" s="18"/>
     <row r="142" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6150,7 +6150,51 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="15.75" customHeight="1" s="18"/>
+    <row r="140" ht="15.75" customHeight="1" s="18">
+      <c r="A140" s="23" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>県議会の親子教室で気づいた「当たり前の日常」のありがたさ</t>
+        </is>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="inlineStr">
+        <is>
+          <t>2028/12/11</t>
+        </is>
+      </c>
+      <c r="E140" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">県議会の親子教室に参加してきました🏛
+実際の議会場に入り、議員さんに直接質問できる貴重な体験。
+長男の質問「議員に休みはありますか？」への答えは
+「公務以外の日も住民の声を聞いています。
+自分も小6の親だけれど、家族旅行にも行けていません」
+市民のために尽力している人がいることを知り、
+同時に、家族と過ごせる休日のありがたさに気づきました。
+朝起きて「おはよう」と言える日常に感謝✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="141" ht="15.75" customHeight="1" s="18"/>
     <row r="142" ht="15.75" customHeight="1" s="18"/>
     <row r="143" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6195,7 +6195,52 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="15.75" customHeight="1" s="18"/>
+    <row r="141" ht="15.75" customHeight="1" s="18">
+      <c r="A141" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="21" t="inlineStr">
+        <is>
+          <t>介護度が低いほど困ることがある。訪問看護師が県議会の仕事に興味を持った理由</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/08</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="inlineStr">
+        <is>
+          <t>2028/12/18</t>
+        </is>
+      </c>
+      <c r="E141" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">介護度が低いほど、困ることがあります🏠
+訪問看護の現場で感じている3つのこと。
+①介護度と「必要な支援の量」は一致しない
+②「孤独」へのフォーマルな支援がない
+③まだまだ同居家族のサポートありきの制度
+どれも事業所や個人の努力では越えられない壁です。
+県議会の親子教室に参加して、
+「制度をつくる側にも人がいる」と実感しました。
+関係ないと思っていた世界が、実は地続きだったんです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="142" ht="15.75" customHeight="1" s="18"/>
     <row r="143" ht="15.75" customHeight="1" s="18"/>
     <row r="144" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6241,7 +6241,53 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="15.75" customHeight="1" s="18"/>
+    <row r="142" ht="15.75" customHeight="1" s="18">
+      <c r="A142" s="23" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="23" t="inlineStr">
+        <is>
+          <t>「自分のために時間を使いたいんだ」小6長男の名言、その実態はゲーム三昧</t>
+        </is>
+      </c>
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>2028/12/25</t>
+        </is>
+      </c>
+      <c r="E142" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「自分のために時間を使いたいんだ」😌
+夏休みも半分。
+長女は友達と映画、次男は友達の家へ。
+でもスマホを持っている長男は、誰とも約束せず…
+「友達と思い出作ったら？」と声をかけたら、
+夕暮れの中で真顔の名言が飛び出しました。
+かっこよく決まってますが、
+あなた宿題もやらずにゲーム三昧ですよ！😂
+長男「だって俺、ゲーマーだから」ニッコリ✌️
+宿題、間に合うのでしょうか…
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="143" ht="15.75" customHeight="1" s="18"/>
     <row r="144" ht="15.75" customHeight="1" s="18"/>
     <row r="145" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6288,7 +6288,52 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="15.75" customHeight="1" s="18"/>
+    <row r="143" ht="15.75" customHeight="1" s="18">
+      <c r="A143" s="21" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="21" t="inlineStr">
+        <is>
+          <t>アイスが却下されて「俺は帰る」。小6長男を一人で歩かせた日の複雑な気持ち</t>
+        </is>
+      </c>
+      <c r="C143" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="D143" s="22" t="inlineStr">
+        <is>
+          <t>2029/01/01</t>
+        </is>
+      </c>
+      <c r="E143" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「俺は帰る」小6長男を一人で歩かせた日🌆
+映画の帰り、アイスの希望が却下されて天邪鬼が発動。
+お金も持たず、バスにも一人で乗ったことがない長男。
+国道を歩けば帰れる道のりを知っていたので、
+国道まで送り、夫と連携して見送りました。
+無事に帰宅してほっとしたけれど、
+この判断で良かったのか、今も答えは出ません。
+帰宅後、長男は自分で気づいてみんなに謝りました。
+これも成長なのかな…複雑な気持ちの1日でした。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="144" ht="15.75" customHeight="1" s="18"/>
     <row r="145" ht="15.75" customHeight="1" s="18"/>
     <row r="146" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6334,7 +6334,51 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="15.75" customHeight="1" s="18"/>
+    <row r="144" ht="15.75" customHeight="1" s="18">
+      <c r="A144" s="23" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="23" t="inlineStr">
+        <is>
+          <t>「お母さんとだと話しかけづらい」長女の初・友達映画で知った子どもの楽しみ方</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="inlineStr">
+        <is>
+          <t>2029/01/08</t>
+        </is>
+      </c>
+      <c r="E144" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「お母さんとだと話しかけづらい」🎬
+長女が初めて友達と映画へ！
+前日から「楽しみー」、当日は5時半起きで服選び😊
+帰ってきて教えてくれたのは、
+「友達と行くと話しかけてもらえて楽しい」ということ。
+映画は静かに見るものだと思い込んでいたけれど、
+子どもにとっては面白い瞬間をすぐ共有するのが楽しいんですね。
+大人と子どもで、映画の面白さは違うんだと知りました✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新
+ご覧いただきありがとうございます！
+3人育児のドタバタ日常を発信中！
+他の投稿もチェックしてみてね
+♥ いいね嬉しいです！　　📌 保存して見返してね！
+</t>
+        </is>
+      </c>
+    </row>
     <row r="145" ht="15.75" customHeight="1" s="18"/>
     <row r="146" ht="15.75" customHeight="1" s="18"/>
     <row r="147" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6340,7 +6340,7 @@
       </c>
       <c r="B144" s="23" t="inlineStr">
         <is>
-          <t>「お母さんとだと話しかけづらい」長女の初・友達映画で知った子どもの楽しみ方</t>
+          <t>「お母さんとだと話しかけづらい」長女の初・友達映画と、100均ネイルの女子力</t>
         </is>
       </c>
       <c r="C144" s="23" t="inlineStr">
@@ -6368,6 +6368,9 @@
 映画は静かに見るものだと思い込んでいたけれど、
 子どもにとっては面白い瞬間をすぐ共有するのが楽しいんですね。
 大人と子どもで、映画の面白さは違うんだと知りました✨
+そして映画のあとは100均でネイルチップをデコって、
+テーマ「海」の力作を披露してくれました💅
+小学生の頃ネイルに1mmも興味がなかった母、脱帽です
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
 #子育てブログ #育児日記 #3人育児 #ドタバタ育児 #育児あるある #小学生ママ #ワーキングマザー #訪問看護師ママ #ブログ更新

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6382,7 +6382,48 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="15.75" customHeight="1" s="18"/>
+    <row r="145" ht="15.75" customHeight="1" s="18">
+      <c r="A145" s="21" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="21" t="inlineStr">
+        <is>
+          <t>「最近、俺すごくない？」お手伝いが定着した夏休み。自信のなかった長男が変わった理由</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="n"/>
+      <c r="D145" s="22" t="inlineStr">
+        <is>
+          <t>2029/01/15</t>
+        </is>
+      </c>
+      <c r="E145" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>夏休みのお手伝い、定着してきました🧹
+母「掃除機お願いします」
+長男「わかりましたー！」
+母「洗濯お願いします」
+長女「はーい！」
+パパ「お風呂掃除するよー」
+次男「ちょっと待ってー」
+…次男、しばらく来ませんけどね😂
+声かけは必要だし、完璧でもない。
+それでも自信のなかった長男が
+「最近、俺すごくない？？」
+とニコニコ報告してくるように✨
+小さな「できた」を自分で認識する
+→ 続ける → 小さな成功 → 自信
+自信ってこうやって育つのかも。
+いっぱい褒めていきたいです☺️
+#3人育児 #小学生ママ #お手伝い #夏休み #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="146" ht="15.75" customHeight="1" s="18"/>
     <row r="147" ht="15.75" customHeight="1" s="18"/>
     <row r="148" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6424,7 +6424,48 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="15.75" customHeight="1" s="18"/>
+    <row r="146" ht="15.75" customHeight="1" s="18">
+      <c r="A146" s="23" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="23" t="inlineStr">
+        <is>
+          <t>「お母さん歯が抜けたよー」次男の報告ポーズが独特すぎて、何度見ても笑ってしまう</t>
+        </is>
+      </c>
+      <c r="C146" s="23" t="n"/>
+      <c r="D146" s="22" t="inlineStr">
+        <is>
+          <t>2029/01/22</t>
+        </is>
+      </c>
+      <c r="E146" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F146" s="23" t="inlineStr">
+        <is>
+          <t>次男の歯が抜けました🦷
+朝グラグラしていた上の歯が
+帰ったら案の定なくなっていました。
+前歯2本は永久歯、その両隣が同時に抜けて
+まるでチップとデールのチップみたい☺️
+そして報告のたびに繰り出される決めポーズ。
+①人差し指を立てる
+②にーっと歯を見せる
+③斜め上を見る
+指はビシッとキマっているのに
+顔はなぜか子泣き爺😂
+何度も同じポーズで報告してくれました。
+次男、成長おめでとう。
+これから生えてくる大人の歯も大事にしようね✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #乳歯 #歯が抜けた #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="147" ht="15.75" customHeight="1" s="18"/>
     <row r="148" ht="15.75" customHeight="1" s="18"/>
     <row r="149" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6466,7 +6466,48 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="15.75" customHeight="1" s="18"/>
+    <row r="147" ht="15.75" customHeight="1" s="18">
+      <c r="A147" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="21" t="inlineStr">
+        <is>
+          <t>出会って30年、なのに「先週会った？」高校の同級生と1年ぶりに飲んだお盆の夜</t>
+        </is>
+      </c>
+      <c r="C147" s="21" t="n"/>
+      <c r="D147" s="22" t="inlineStr">
+        <is>
+          <t>2029/01/29</t>
+        </is>
+      </c>
+      <c r="E147" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F147" s="21" t="inlineStr">
+        <is>
+          <t>お盆の帰省に合わせて、
+高校の友達と1年ぶりに集まりました🍻
+出会って30年くらい経つのに、
+席に着いた瞬間から先週会った感覚。
+空白を埋める作業が要らない関係、ありがたいです。
+友人の子はもう高校生・中学生。
+私立か公立かは「子どもの個性による」
+——実際に通った人の話は重みが違いました。
+そして盛り上がる子育てあるある。
+「同じ環境なのに性格は全然違うよねー」
+「男の子って片付けとか丁寧にとか皆無だよねー」
+うちだけじゃないんだなぁと
+日々のイライラがすこーし和らぎました☺️
+じゃあ、また来年ー！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #ワーママ #同級生 #お盆 #帰省 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="148" ht="15.75" customHeight="1" s="18"/>
     <row r="149" ht="15.75" customHeight="1" s="18"/>
     <row r="150" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6508,7 +6508,52 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="15.75" customHeight="1" s="18"/>
+    <row r="148" ht="15.75" customHeight="1" s="18">
+      <c r="A148" s="23" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="23" t="inlineStr">
+        <is>
+          <t>「やる気は動いてからしか出ません」夏休みの宿題、3人3様のサポートが必要だった話</t>
+        </is>
+      </c>
+      <c r="C148" s="23" t="n"/>
+      <c r="D148" s="22" t="inlineStr">
+        <is>
+          <t>2029/02/05</t>
+        </is>
+      </c>
+      <c r="E148" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F148" s="23" t="inlineStr">
+        <is>
+          <t>お盆時点の宿題進捗📝
+長男50% / 長女90% / 次男85%
+読書感想文は全員まだ…！
+同じ家で同じように育てているのに
+動き出すきっかけは3人とも全然違います。
+🔹次男(小1)
+とにかく始めるハードルを下げる。
+朝顔の水やりもペットボトルに水を入れて
+「さぁすぐできますよ」の状態でバトンタッチ。
+🔹長男(小6)
+優先順位を一緒に整理する。
+「やる気は動いてからしか出ません」が口ぐせです。
+🔹長女(小4)
+褒めて評価しまくる。
+「やっぱりすごいな」でモチベ維持。
+一律に声をかけて待つのは
+一見ラクだけど誰にも届かない。
+個に合わせた関わりが結局は一番早い✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #夏休みの宿題 #夏休み #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="149" ht="15.75" customHeight="1" s="18"/>
     <row r="150" ht="15.75" customHeight="1" s="18"/>
     <row r="151" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6554,7 +6554,50 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="15.75" customHeight="1" s="18"/>
+    <row r="149" ht="15.75" customHeight="1" s="18">
+      <c r="A149" s="21" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="21" t="inlineStr">
+        <is>
+          <t>「字は上手じゃなくてもいいんだよ」小4長女の声かけが、母よりずっと上手だった日</t>
+        </is>
+      </c>
+      <c r="C149" s="21" t="n"/>
+      <c r="D149" s="22" t="inlineStr">
+        <is>
+          <t>2029/02/12</t>
+        </is>
+      </c>
+      <c r="E149" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F149" s="21" t="inlineStr">
+        <is>
+          <t>お盆終盤、読書感想文との格闘📖
+長女(小4)は午前に下書き、午後は清書と順調。
+次男(小1)は午前中に書けたのが
+本の名前と自分の名前だけ…！
+「目が眩しいから書けない」→サングラス
+「牛乳を飲んでから」→コップに注いで運ぶ
+このお膳立て、ほぼ長女がやってくれました。
+私は内心「どんどんやれば終わるのに」とイライラ。
+でも長女は違いました。
+長女「何が嫌なの？」
+次男「字が上手に書けないから」
+長女「大丈夫だよ、字は上手じゃなくてもいいんだよ。
+　　　これは本を読んだ感想を書くだけだから」
+私は結果を急いで、長女は理由を聞いた。
+小4に教わってしまいました😌
+長女の接し方を参考に、伴走していきます。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #読書感想文 #夏休みの宿題 #きょうだい #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="150" ht="15.75" customHeight="1" s="18"/>
     <row r="151" ht="15.75" customHeight="1" s="18"/>
     <row r="152" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6598,7 +6598,52 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="15.75" customHeight="1" s="18"/>
+    <row r="150" ht="15.75" customHeight="1" s="18">
+      <c r="A150" s="23" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="23" t="inlineStr">
+        <is>
+          <t>洗濯洗剤vs食器用洗剤、小6長男が次男の激臭靴下で比較実験した家庭科の宿題</t>
+        </is>
+      </c>
+      <c r="C150" s="23" t="n"/>
+      <c r="D150" s="22" t="inlineStr">
+        <is>
+          <t>2029/02/19</t>
+        </is>
+      </c>
+      <c r="E150" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F150" s="23" t="inlineStr">
+        <is>
+          <t>長男の家庭科の宿題「汚れ物の手洗い」🧦
+いつでもやれたはずなのに放置。長男らしい…
+今日は外出してお昼を食べて公園で遊んで帰宅。
+そして帰ってきた次男の靴下。
+外出後の異臭がすごいんです。
+恰好の餌食、爆誕😂
+しかもここから長男が動きました。
+以前ミートソースの汚れが
+食器用洗剤で落ちたことを覚えていて
+「食器用洗剤も使ってみたい」と。
+片方は洗濯洗剤、もう片方は食器用洗剤。
+左右の靴下で比較実験です✨
+【結果】
+匂い → 両方とも消えた
+汚れ → 洗濯洗剤の方が取れた
+洗った靴下はピンチで風に揺れています。
+洗ったのはあの雑な長男。
+勇気を出して匂いを確認してきます…！
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #夏休みの宿題 #家庭科 #小学6年生 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="151" ht="15.75" customHeight="1" s="18"/>
     <row r="152" ht="15.75" customHeight="1" s="18"/>
     <row r="153" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6632,12 +6632,18 @@
 「食器用洗剤も使ってみたい」と。
 片方は洗濯洗剤、もう片方は食器用洗剤。
 左右の靴下で比較実験です✨
-【結果】
-匂い → 両方とも消えた
-汚れ → 洗濯洗剤の方が取れた
-洗った靴下はピンチで風に揺れています。
-洗ったのはあの雑な長男。
-勇気を出して匂いを確認してきます…！
+【洗った直後】
+匂いの差はなし。汚れは洗濯洗剤の勝ち。
+【乾いたあと】
+洗濯洗剤 → 匂いなし
+食器用洗剤 → 臭う！！
+まったくの別物でした😱
+匂いの判定は乾いてからです。
+長男も違いをはっきり認識し
+嬉しそうにパソコンに結果を打ち込んでいました✨
+家庭科の宿題、これでコンプリート！
+残すは読書感想文。達成度20%。
+夏休みはあと8日。頑張れ長男…！
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
 #3人育児 #小学生ママ #夏休みの宿題 #家庭科 #小学6年生 #子育て日記 #ドタバタ母さん</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6650,7 +6650,52 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="15.75" customHeight="1" s="18"/>
+    <row r="151" ht="15.75" customHeight="1" s="18">
+      <c r="A151" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>「お前も鬼にならないかぁ？」サッカーのゴールキーパー中に、小1次男が鬼と化していた</t>
+        </is>
+      </c>
+      <c r="C151" s="21" t="n"/>
+      <c r="D151" s="22" t="inlineStr">
+        <is>
+          <t>2029/02/26</t>
+        </is>
+      </c>
+      <c r="E151" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t>サッカー練習のお迎えでの出来事⚽
+ゴールキーパーをやっている次男を発見。
+でも私の知っているキーパーの
+立ち振る舞いではありませんでした。
+そして聞こえてきたのです。
+結構なボリュームで。
+「お前も鬼にならないかぁ？」
+完全に猗窩座😇
+まだボールが迫っていなかったので
+誰ひとり気づいていません。
+みんなが必死にボールを追いかける中
+彼だけ完全に別次元の鬼。
+恥ずかしいやら、おかしいやら…！
+その後も鬼になるタイミングがあれば
+凄みを効かせて勧誘を続けていました。
+（誰も入団しませんでしたが）
+ボールが来ない時間、
+頭の中では別の物語が進行しているようです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #サッカー少年 #なりきり #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="152" ht="15.75" customHeight="1" s="18"/>
     <row r="153" ht="15.75" customHeight="1" s="18"/>
     <row r="154" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6690,6 +6690,10 @@
 （誰も入団しませんでしたが）
 ボールが来ない時間、
 頭の中では別の物語が進行しているようです。
+ちなみに「鬼とボール」といえば浅草編。
+手毬鬼・朱紗丸は巨大な手毬を蹴って攻撃します。
+鬼が、球を、蹴る。
+…案外、理にかなっていたのかも？🤔
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
 #3人育児 #小学生ママ #小学1年生 #サッカー少年 #なりきり #子育て日記 #ドタバタ母さん</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6700,7 +6700,59 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="15.75" customHeight="1" s="18"/>
+    <row r="152" ht="15.75" customHeight="1" s="18">
+      <c r="A152" s="23" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="23" t="inlineStr">
+        <is>
+          <t>「今日やる」と言って何もせず1週間。小6長男の読書感想文が動き出した日</t>
+        </is>
+      </c>
+      <c r="C152" s="23" t="n"/>
+      <c r="D152" s="22" t="inlineStr">
+        <is>
+          <t>2029/03/05</t>
+        </is>
+      </c>
+      <c r="E152" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F152" s="23" t="inlineStr">
+        <is>
+          <t>読書感想文が終わりません📖
+朝「今日やる」と言い、
+帰ると何もやっていない。
+それを繰り返して1週間。
+学校開始まであと2日…！
+長男「今日まですっかり忘れてた」
+私（んな訳あるかー！！）
+でも本人がそう言うなら。
+「思い出した今からやればいいのでは」
+と伝えると泣きそうな表情に。
+なんの涙かは本人も分からず。
+話していくうちに分かったこと。
+・本は何度も読んでいる
+・気になった箇所も決まっている
+・自分の経験もしっかりある
+材料は全部そろっていました。
+できないのは「アウトプット」だったのです。
+そこで構成を一緒に確認📝
+①はじめに(本の紹介)
+②気になった箇所を2〜3つ
+③その理由と感じたこと
+④自分の経験を入れてまとめ
+説明するうちに頷きが増えてきた長男。
+ようやくエンジンがかかりました✨
+頑張れ長男。あなたはできる。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #読書感想文 #夏休みの宿題 #小学6年生 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="153" ht="15.75" customHeight="1" s="18"/>
     <row r="154" ht="15.75" customHeight="1" s="18"/>
     <row r="155" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>「俺、今日やばかったよ！」と豪語する6歳次男。ドヤ顔で報告してきた順位は、まさかの11位‼︎</t>
+          <t>【爆笑】「まじやばかったよ」とドヤ顔で帰宅した6歳次男の、斜め上すぎる報告</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>11歳男子の管理能力とは？キャッシュカードを手に入れた男の末路</t>
+          <t>【静かなる実験】自立宣言から一週間。長男が「全財産」を失ったことに気づくのはいつか？</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2026/01/19</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>歌舞伎の「見得」を披露したら、小３長女の眼差しが一変した朝の話</t>
+          <t>歌舞伎の見得を伝授した結果、娘は一生成功を確認できなくなった話</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>2026/03/08</t>
+          <t>2026/03/07</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>次男の「お風呂スタメン」に隠された、謎すぎる選考基準</t>
+          <t>🛁 次男の「お風呂スタメン」に隠された、謎すぎる選考基準</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026/03/20</t>
+          <t>2026/06/04</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2240,8 +2240,10 @@
           <t>筆箱の中に「しらす」がいた日―子どもの発想力に脱帽した話</t>
         </is>
       </c>
-      <c r="C44" s="9" t="n">
-        <v>46133</v>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
       </c>
       <c r="D44" s="9" t="n">
         <v>46426</v>
@@ -2431,7 +2433,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/07/02</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -2509,7 +2511,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -2587,7 +2589,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -2626,7 +2628,7 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/07/09</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -2782,7 +2784,7 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -2821,7 +2823,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -2860,7 +2862,7 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2938,7 +2940,7 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>2026/05/24</t>
+          <t>2026/07/28</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -3016,7 +3018,7 @@
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>2026/05/31</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -3055,7 +3057,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>2026/05/31</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -3133,7 +3135,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -4030,7 +4032,7 @@
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/08/24</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -4771,7 +4773,7 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="D109" s="22" t="inlineStr">
@@ -4989,7 +4991,7 @@
       </c>
       <c r="C114" s="23" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="D114" s="22" t="inlineStr">
@@ -5033,7 +5035,7 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="D115" s="22" t="inlineStr">
@@ -5210,7 +5212,7 @@
       </c>
       <c r="C119" s="21" t="inlineStr">
         <is>
-          <t>2026/07/11</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="D119" s="22" t="inlineStr">
@@ -5255,7 +5257,7 @@
       </c>
       <c r="C120" s="23" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="D120" s="22" t="inlineStr">
@@ -5523,7 +5525,7 @@
       </c>
       <c r="C126" s="23" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="D126" s="22" t="inlineStr">
@@ -5745,12 +5747,12 @@
       </c>
       <c r="B131" s="21" t="inlineStr">
         <is>
-          <t>「お母さん、すごくない？」半紙パンパンの書道バッグを見て、長男の整理の概念が崩壊していた話</t>
+          <t>「お母さん、すごくない？」半紙パンパンの書道バッグを見て、長男の「整理」の概念が崩壊していた話</t>
         </is>
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="D131" s="22" t="inlineStr">
@@ -5978,7 +5980,7 @@
       </c>
       <c r="C136" s="23" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/01</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
@@ -6023,7 +6025,7 @@
       </c>
       <c r="C137" s="21" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/01</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
@@ -6161,7 +6163,7 @@
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>2026/08/08</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="D140" s="22" t="inlineStr">
@@ -6206,7 +6208,7 @@
       </c>
       <c r="C141" s="21" t="inlineStr">
         <is>
-          <t>2026/08/08</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="D141" s="22" t="inlineStr">
@@ -6299,7 +6301,7 @@
       </c>
       <c r="C143" s="21" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/08</t>
         </is>
       </c>
       <c r="D143" s="22" t="inlineStr">
@@ -6345,7 +6347,7 @@
       </c>
       <c r="C144" s="23" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/10</t>
         </is>
       </c>
       <c r="D144" s="22" t="inlineStr">
@@ -6391,7 +6393,11 @@
           <t>「最近、俺すごくない？」お手伝いが定着した夏休み。自信のなかった長男が変わった理由</t>
         </is>
       </c>
-      <c r="C145" s="21" t="n"/>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
           <t>2029/01/15</t>
@@ -6475,7 +6481,11 @@
           <t>出会って30年、なのに「先週会った？」高校の同級生と1年ぶりに飲んだお盆の夜</t>
         </is>
       </c>
-      <c r="C147" s="21" t="n"/>
+      <c r="C147" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
       <c r="D147" s="22" t="inlineStr">
         <is>
           <t>2029/01/29</t>
@@ -6517,7 +6527,11 @@
           <t>「やる気は動いてからしか出ません」夏休みの宿題、3人3様のサポートが必要だった話</t>
         </is>
       </c>
-      <c r="C148" s="23" t="n"/>
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
           <t>2029/02/05</t>
@@ -6563,7 +6577,11 @@
           <t>「字は上手じゃなくてもいいんだよ」小4長女の声かけが、母よりずっと上手だった日</t>
         </is>
       </c>
-      <c r="C149" s="21" t="n"/>
+      <c r="C149" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
           <t>2029/02/12</t>
@@ -6607,7 +6625,11 @@
           <t>洗濯洗剤vs食器用洗剤、小6長男が次男の激臭靴下で比較実験した家庭科の宿題</t>
         </is>
       </c>
-      <c r="C150" s="23" t="n"/>
+      <c r="C150" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
           <t>2029/02/19</t>
@@ -6709,7 +6731,11 @@
           <t>「今日やる」と言って何もせず1週間。小6長男の読書感想文が動き出した日</t>
         </is>
       </c>
-      <c r="C152" s="23" t="n"/>
+      <c r="C152" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
       <c r="D152" s="22" t="inlineStr">
         <is>
           <t>2029/03/05</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/05</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>2026/09/21</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>2026/09/28</t>
+          <t>2026/09/26</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>2026/10/05</t>
+          <t>2026/10/03</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/10</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>2026/10/19</t>
+          <t>2026/10/17</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/10/24</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/10/31</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>2026/11/09</t>
+          <t>2026/11/07</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2026/11/14</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/12/05</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2026/12/12</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2026/12/19</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>2026/12/26</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>2027/01/04</t>
+          <t>2027/01/02</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/09</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2027/01/16</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>2027/01/25</t>
+          <t>2027/01/23</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2245,8 +2245,10 @@
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
-        <v>46426</v>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/06</t>
+        </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -2282,7 +2284,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>2027/02/15</t>
+          <t>2027/02/13</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -2321,7 +2323,7 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>2027/02/22</t>
+          <t>2027/02/20</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
@@ -2360,7 +2362,7 @@
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>2027/03/01</t>
+          <t>2027/02/27</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -2399,7 +2401,7 @@
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>2027/03/08</t>
+          <t>2027/03/06</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
@@ -2438,7 +2440,7 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>2027/03/15</t>
+          <t>2027/03/13</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -2477,7 +2479,7 @@
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>2027/03/22</t>
+          <t>2027/03/20</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
@@ -2516,7 +2518,7 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>2027/03/29</t>
+          <t>2027/03/27</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -2555,7 +2557,7 @@
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>2027/04/05</t>
+          <t>2027/04/03</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
@@ -2594,7 +2596,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>2027/04/12</t>
+          <t>2027/04/10</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2633,7 +2635,7 @@
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>2027/04/19</t>
+          <t>2027/04/17</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
@@ -2672,7 +2674,7 @@
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>2027/04/26</t>
+          <t>2027/04/24</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -2711,7 +2713,7 @@
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>2027/05/03</t>
+          <t>2027/05/01</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
@@ -2750,7 +2752,7 @@
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>2027/05/10</t>
+          <t>2027/05/08</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -2789,7 +2791,7 @@
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>2027/05/17</t>
+          <t>2027/05/15</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
@@ -2828,7 +2830,7 @@
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>2027/05/24</t>
+          <t>2027/05/22</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2867,7 +2869,7 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>2027/05/31</t>
+          <t>2027/05/29</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
@@ -2906,7 +2908,7 @@
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>2027/06/07</t>
+          <t>2027/06/05</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2945,7 +2947,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>2027/06/14</t>
+          <t>2027/06/12</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -2984,7 +2986,7 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2027/06/19</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3023,7 +3025,7 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>2027/06/28</t>
+          <t>2027/06/26</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
@@ -3062,7 +3064,7 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>2027/07/05</t>
+          <t>2027/07/03</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3101,7 +3103,7 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>2027/07/12</t>
+          <t>2027/07/10</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -3140,7 +3142,7 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>2027/07/19</t>
+          <t>2027/07/17</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3179,7 +3181,7 @@
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>2027/07/26</t>
+          <t>2027/07/24</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
@@ -3218,7 +3220,7 @@
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>2027/08/02</t>
+          <t>2027/07/31</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3257,7 +3259,7 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>2027/08/09</t>
+          <t>2027/08/07</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
@@ -3296,7 +3298,7 @@
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>2027/08/16</t>
+          <t>2027/08/14</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3335,7 +3337,7 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>2027/08/23</t>
+          <t>2027/08/21</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
@@ -3374,7 +3376,7 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>2027/08/30</t>
+          <t>2027/08/28</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3413,7 +3415,7 @@
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>2027/09/06</t>
+          <t>2027/09/04</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
@@ -3452,7 +3454,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>2027/09/13</t>
+          <t>2027/09/11</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3491,7 +3493,7 @@
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>2027/09/20</t>
+          <t>2027/09/18</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
@@ -3530,7 +3532,7 @@
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>2027/09/27</t>
+          <t>2027/09/25</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3569,7 +3571,7 @@
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>2027/10/04</t>
+          <t>2027/10/02</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
@@ -3608,7 +3610,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>2027/10/11</t>
+          <t>2027/10/09</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3647,7 +3649,7 @@
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>2027/10/18</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
@@ -3686,7 +3688,7 @@
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>2027/10/25</t>
+          <t>2027/10/23</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3725,7 +3727,7 @@
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>2027/11/01</t>
+          <t>2027/10/30</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
@@ -3764,7 +3766,7 @@
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>2027/11/08</t>
+          <t>2027/11/06</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -3803,7 +3805,7 @@
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>2027/11/15</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
@@ -3842,7 +3844,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>2027/11/22</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -3881,7 +3883,7 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>2027/11/29</t>
+          <t>2027/11/27</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
@@ -3920,7 +3922,7 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>2027/12/06</t>
+          <t>2027/12/04</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -3959,7 +3961,7 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>2027/12/13</t>
+          <t>2027/12/11</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
@@ -3998,7 +4000,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>2027/12/18</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4037,7 +4039,7 @@
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>2027/12/27</t>
+          <t>2027/12/25</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
@@ -4076,7 +4078,7 @@
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>2028/01/03</t>
+          <t>2028/01/01</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
@@ -4115,7 +4117,7 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>2028/01/10</t>
+          <t>2028/01/08</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
@@ -4154,7 +4156,7 @@
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>2028/01/17</t>
+          <t>2028/01/15</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
@@ -4193,7 +4195,7 @@
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>2028/01/24</t>
+          <t>2028/01/22</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
@@ -4232,7 +4234,7 @@
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>2028/01/31</t>
+          <t>2028/01/29</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -4271,7 +4273,7 @@
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>2028/02/07</t>
+          <t>2028/02/05</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
@@ -4310,7 +4312,7 @@
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>2028/02/14</t>
+          <t>2028/02/12</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
@@ -4349,7 +4351,7 @@
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>2028/02/21</t>
+          <t>2028/02/19</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
@@ -4388,7 +4390,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2028/02/28</t>
+          <t>2028/02/26</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4427,7 +4429,7 @@
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>2028/03/06</t>
+          <t>2028/03/04</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
@@ -4466,7 +4468,7 @@
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2028/03/11</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4505,7 +4507,7 @@
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>2028/03/20</t>
+          <t>2028/03/18</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
@@ -4544,7 +4546,7 @@
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>2028/03/27</t>
+          <t>2028/03/25</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
@@ -4583,7 +4585,7 @@
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>2028/04/03</t>
+          <t>2028/04/01</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
@@ -4622,7 +4624,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>2028/04/10</t>
+          <t>2028/04/08</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -4661,7 +4663,7 @@
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>2028/04/17</t>
+          <t>2028/04/15</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -4700,7 +4702,7 @@
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>2028/04/24</t>
+          <t>2028/04/22</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
@@ -4739,7 +4741,7 @@
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>2028/05/01</t>
+          <t>2028/04/29</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -4778,7 +4780,7 @@
       </c>
       <c r="D109" s="22" t="inlineStr">
         <is>
-          <t>2028/05/08</t>
+          <t>2028/05/06</t>
         </is>
       </c>
       <c r="E109" s="21" t="inlineStr">
@@ -4820,7 +4822,7 @@
       </c>
       <c r="D110" s="22" t="inlineStr">
         <is>
-          <t>2028/05/15</t>
+          <t>2028/05/13</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
@@ -4866,7 +4868,7 @@
       </c>
       <c r="D111" s="22" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2028/05/20</t>
         </is>
       </c>
       <c r="E111" s="21" t="inlineStr">
@@ -4909,7 +4911,7 @@
       </c>
       <c r="D112" s="22" t="inlineStr">
         <is>
-          <t>2028/05/29</t>
+          <t>2028/05/27</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
@@ -4952,7 +4954,7 @@
       </c>
       <c r="D113" s="22" t="inlineStr">
         <is>
-          <t>2028/06/05</t>
+          <t>2028/06/03</t>
         </is>
       </c>
       <c r="E113" s="21" t="inlineStr">
@@ -4996,7 +4998,7 @@
       </c>
       <c r="D114" s="22" t="inlineStr">
         <is>
-          <t>2028/06/12</t>
+          <t>2028/06/10</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
@@ -5040,7 +5042,7 @@
       </c>
       <c r="D115" s="22" t="inlineStr">
         <is>
-          <t>2028/06/19</t>
+          <t>2028/06/17</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -5083,7 +5085,7 @@
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2028/06/26</t>
+          <t>2028/06/24</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -5128,7 +5130,7 @@
       </c>
       <c r="D117" s="22" t="inlineStr">
         <is>
-          <t>2028/07/03</t>
+          <t>2028/07/01</t>
         </is>
       </c>
       <c r="E117" s="21" t="inlineStr">
@@ -5172,7 +5174,7 @@
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>2028/07/10</t>
+          <t>2028/07/08</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
@@ -5217,7 +5219,7 @@
       </c>
       <c r="D119" s="22" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2028/07/15</t>
         </is>
       </c>
       <c r="E119" s="21" t="inlineStr">
@@ -5262,7 +5264,7 @@
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>2028/07/24</t>
+          <t>2028/07/22</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
@@ -5306,7 +5308,7 @@
       </c>
       <c r="D121" s="22" t="inlineStr">
         <is>
-          <t>2028/07/31</t>
+          <t>2028/07/29</t>
         </is>
       </c>
       <c r="E121" s="21" t="inlineStr">
@@ -5351,7 +5353,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2028/08/05</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -5396,7 +5398,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2028/08/12</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5441,7 +5443,7 @@
       </c>
       <c r="D124" s="22" t="inlineStr">
         <is>
-          <t>2028/08/21</t>
+          <t>2028/08/19</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
@@ -5485,7 +5487,7 @@
       </c>
       <c r="D125" s="22" t="inlineStr">
         <is>
-          <t>2028/08/28</t>
+          <t>2028/08/26</t>
         </is>
       </c>
       <c r="E125" s="21" t="inlineStr">
@@ -5530,7 +5532,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>2028/09/04</t>
+          <t>2028/09/02</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
@@ -5576,7 +5578,7 @@
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>2028/09/11</t>
+          <t>2028/09/09</t>
         </is>
       </c>
       <c r="E127" s="21" t="inlineStr">
@@ -5621,7 +5623,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>2028/09/18</t>
+          <t>2028/09/16</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
@@ -5666,7 +5668,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/09/23</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -5711,7 +5713,7 @@
       </c>
       <c r="D130" s="22" t="inlineStr">
         <is>
-          <t>2028/10/02</t>
+          <t>2028/09/30</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
@@ -5757,7 +5759,7 @@
       </c>
       <c r="D131" s="22" t="inlineStr">
         <is>
-          <t>2028/10/09</t>
+          <t>2028/10/07</t>
         </is>
       </c>
       <c r="E131" s="21" t="inlineStr">
@@ -5804,7 +5806,7 @@
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>2028/10/16</t>
+          <t>2028/10/14</t>
         </is>
       </c>
       <c r="E132" s="21" t="inlineStr">
@@ -5849,7 +5851,7 @@
       </c>
       <c r="D133" s="22" t="inlineStr">
         <is>
-          <t>2028/10/23</t>
+          <t>2028/10/21</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
@@ -5895,7 +5897,7 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>2028/10/30</t>
+          <t>2028/10/28</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
@@ -5939,7 +5941,7 @@
       </c>
       <c r="D135" s="22" t="inlineStr">
         <is>
-          <t>2028/11/06</t>
+          <t>2028/11/04</t>
         </is>
       </c>
       <c r="E135" s="21" t="inlineStr">
@@ -5985,7 +5987,7 @@
       </c>
       <c r="D136" s="22" t="inlineStr">
         <is>
-          <t>2028/11/13</t>
+          <t>2028/11/11</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
@@ -6030,7 +6032,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>2028/11/20</t>
+          <t>2028/11/18</t>
         </is>
       </c>
       <c r="E137" s="21" t="inlineStr">
@@ -6075,7 +6077,7 @@
       </c>
       <c r="D138" s="22" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2028/11/25</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
@@ -6121,7 +6123,7 @@
       </c>
       <c r="D139" s="22" t="inlineStr">
         <is>
-          <t>2028/12/04</t>
+          <t>2028/12/02</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -6168,7 +6170,7 @@
       </c>
       <c r="D140" s="22" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2028/12/09</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
@@ -6213,7 +6215,7 @@
       </c>
       <c r="D141" s="22" t="inlineStr">
         <is>
-          <t>2028/12/18</t>
+          <t>2028/12/16</t>
         </is>
       </c>
       <c r="E141" s="21" t="inlineStr">
@@ -6259,7 +6261,7 @@
       </c>
       <c r="D142" s="22" t="inlineStr">
         <is>
-          <t>2028/12/25</t>
+          <t>2028/12/23</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
@@ -6306,7 +6308,7 @@
       </c>
       <c r="D143" s="22" t="inlineStr">
         <is>
-          <t>2029/01/01</t>
+          <t>2028/12/30</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -6352,7 +6354,7 @@
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/06</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -6400,7 +6402,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>2029/01/15</t>
+          <t>2029/01/13</t>
         </is>
       </c>
       <c r="E145" s="21" t="inlineStr">
@@ -6442,7 +6444,7 @@
       <c r="C146" s="23" t="n"/>
       <c r="D146" s="22" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2029/01/20</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
@@ -6488,7 +6490,7 @@
       </c>
       <c r="D147" s="22" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2029/01/27</t>
         </is>
       </c>
       <c r="E147" s="21" t="inlineStr">
@@ -6534,7 +6536,7 @@
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2029/02/03</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -6584,7 +6586,7 @@
       </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2029/02/10</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -6632,7 +6634,7 @@
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>2029/02/19</t>
+          <t>2029/02/17</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -6684,7 +6686,7 @@
       <c r="C151" s="21" t="n"/>
       <c r="D151" s="22" t="inlineStr">
         <is>
-          <t>2029/02/26</t>
+          <t>2029/02/24</t>
         </is>
       </c>
       <c r="E151" s="21" t="inlineStr">
@@ -6738,7 +6740,7 @@
       </c>
       <c r="D152" s="22" t="inlineStr">
         <is>
-          <t>2029/03/05</t>
+          <t>2029/03/03</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/04/18</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026/04/27</t>
+          <t>2026/04/25</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/05/02</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026/05/11</t>
+          <t>2026/05/09</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/05/16</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/23</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026/06/08</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/13</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/20</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/06/27</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/25</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/01</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>2026/08/10</t>
+          <t>2026/08/08</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/15</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/22</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/08/29</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 重複のため見送り</t>
         </is>
       </c>
       <c r="F61" s="19" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>2027/06/12</t>
+          <t>2027/06/05</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2027/06/12</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>2027/06/26</t>
+          <t>2027/06/19</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>2027/07/03</t>
+          <t>2027/06/26</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>2027/07/10</t>
+          <t>2027/07/03</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>2027/07/17</t>
+          <t>2027/07/10</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>2027/07/24</t>
+          <t>2027/07/17</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>2027/07/31</t>
+          <t>2027/07/24</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>2027/08/07</t>
+          <t>2027/07/31</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 重複のため見送り</t>
         </is>
       </c>
       <c r="F71" s="19" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>2027/08/21</t>
+          <t>2027/08/07</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>2027/08/28</t>
+          <t>2027/08/14</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>2027/09/04</t>
+          <t>2027/08/21</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>2027/09/11</t>
+          <t>2027/08/28</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>2027/09/18</t>
+          <t>2027/09/04</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>2027/09/25</t>
+          <t>2027/09/11</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>2027/10/02</t>
+          <t>2027/09/18</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>2027/10/09</t>
+          <t>2027/09/25</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/10/02</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>2027/10/23</t>
+          <t>2027/10/09</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
-          <t>2027/10/30</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2027/10/23</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/10/30</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/11/06</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>2027/12/04</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/11/27</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>2027/12/18</t>
+          <t>2027/12/04</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>2027/12/25</t>
+          <t>2027/12/11</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>2028/01/01</t>
+          <t>2027/12/18</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>2028/01/08</t>
+          <t>2027/12/25</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>2028/01/15</t>
+          <t>2028/01/01</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>2028/01/22</t>
+          <t>2028/01/08</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>2028/01/29</t>
+          <t>2028/01/15</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>2028/02/05</t>
+          <t>2028/01/22</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
-          <t>2028/02/12</t>
+          <t>2028/01/29</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/02/05</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2028/02/26</t>
+          <t>2028/02/12</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>2028/03/04</t>
+          <t>2028/02/19</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
-          <t>2028/03/11</t>
+          <t>2028/02/26</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
-          <t>2028/03/18</t>
+          <t>2028/03/04</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
-          <t>2028/03/25</t>
+          <t>2028/03/11</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
-          <t>2028/04/01</t>
+          <t>2028/03/18</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>2028/04/08</t>
+          <t>2028/03/25</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2028/04/01</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
-          <t>2028/04/22</t>
+          <t>2028/04/08</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>2028/04/29</t>
+          <t>2028/04/15</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D109" s="22" t="inlineStr">
         <is>
-          <t>2028/05/06</t>
+          <t>2028/04/22</t>
         </is>
       </c>
       <c r="E109" s="21" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D110" s="22" t="inlineStr">
         <is>
-          <t>2028/05/13</t>
+          <t>2028/04/29</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="D111" s="22" t="inlineStr">
         <is>
-          <t>2028/05/20</t>
+          <t>2028/05/06</t>
         </is>
       </c>
       <c r="E111" s="21" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D112" s="22" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>2028/05/13</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D113" s="22" t="inlineStr">
         <is>
-          <t>2028/06/03</t>
+          <t>2028/05/20</t>
         </is>
       </c>
       <c r="E113" s="21" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D114" s="22" t="inlineStr">
         <is>
-          <t>2028/06/10</t>
+          <t>2028/05/27</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D115" s="22" t="inlineStr">
         <is>
-          <t>2028/06/17</t>
+          <t>2028/06/03</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2028/06/24</t>
+          <t>2028/06/10</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D117" s="22" t="inlineStr">
         <is>
-          <t>2028/07/01</t>
+          <t>2028/06/17</t>
         </is>
       </c>
       <c r="E117" s="21" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>2028/07/08</t>
+          <t>2028/06/24</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="D119" s="22" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2028/07/01</t>
         </is>
       </c>
       <c r="E119" s="21" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>2028/07/22</t>
+          <t>2028/07/08</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D121" s="22" t="inlineStr">
         <is>
-          <t>2028/07/29</t>
+          <t>2028/07/15</t>
         </is>
       </c>
       <c r="E121" s="21" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>2028/08/05</t>
+          <t>2028/07/22</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2028/07/29</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D124" s="22" t="inlineStr">
         <is>
-          <t>2028/08/19</t>
+          <t>2028/08/05</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D125" s="22" t="inlineStr">
         <is>
-          <t>2028/08/26</t>
+          <t>2028/08/12</t>
         </is>
       </c>
       <c r="E125" s="21" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>2028/09/02</t>
+          <t>2028/08/19</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>2028/09/09</t>
+          <t>2028/08/26</t>
         </is>
       </c>
       <c r="E127" s="21" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/09/02</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>2028/09/23</t>
+          <t>2028/09/09</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D130" s="22" t="inlineStr">
         <is>
-          <t>2028/09/30</t>
+          <t>2028/09/16</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D131" s="22" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2028/09/23</t>
         </is>
       </c>
       <c r="E131" s="21" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>2028/10/14</t>
+          <t>2028/09/30</t>
         </is>
       </c>
       <c r="E132" s="21" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D133" s="22" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2028/10/07</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>2028/10/28</t>
+          <t>2028/10/14</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D135" s="22" t="inlineStr">
         <is>
-          <t>2028/11/04</t>
+          <t>2028/10/21</t>
         </is>
       </c>
       <c r="E135" s="21" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="D136" s="22" t="inlineStr">
         <is>
-          <t>2028/11/11</t>
+          <t>2028/10/28</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>2028/11/18</t>
+          <t>2028/11/04</t>
         </is>
       </c>
       <c r="E137" s="21" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D138" s="22" t="inlineStr">
         <is>
-          <t>2028/11/25</t>
+          <t>2028/11/11</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D139" s="22" t="inlineStr">
         <is>
-          <t>2028/12/02</t>
+          <t>2028/11/18</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D140" s="22" t="inlineStr">
         <is>
-          <t>2028/12/09</t>
+          <t>2028/11/25</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D141" s="22" t="inlineStr">
         <is>
-          <t>2028/12/16</t>
+          <t>2028/12/02</t>
         </is>
       </c>
       <c r="E141" s="21" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D142" s="22" t="inlineStr">
         <is>
-          <t>2028/12/23</t>
+          <t>2028/12/09</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D143" s="22" t="inlineStr">
         <is>
-          <t>2028/12/30</t>
+          <t>2028/12/16</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2028/12/23</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>2029/01/13</t>
+          <t>2028/12/30</t>
         </is>
       </c>
       <c r="E145" s="21" t="inlineStr">
@@ -6444,7 +6444,7 @@
       <c r="C146" s="23" t="n"/>
       <c r="D146" s="22" t="inlineStr">
         <is>
-          <t>2029/01/20</t>
+          <t>2029/01/06</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="D147" s="22" t="inlineStr">
         <is>
-          <t>2029/01/27</t>
+          <t>2029/01/13</t>
         </is>
       </c>
       <c r="E147" s="21" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>2029/02/03</t>
+          <t>2029/01/20</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2029/01/27</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>2029/02/17</t>
+          <t>2029/02/03</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -6686,7 +6686,7 @@
       <c r="C151" s="21" t="n"/>
       <c r="D151" s="22" t="inlineStr">
         <is>
-          <t>2029/02/24</t>
+          <t>2029/02/10</t>
         </is>
       </c>
       <c r="E151" s="21" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="D152" s="22" t="inlineStr">
         <is>
-          <t>2029/03/03</t>
+          <t>2029/02/17</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6781,7 +6781,52 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="15.75" customHeight="1" s="18"/>
+    <row r="153" ht="15.75" customHeight="1" s="18">
+      <c r="A153" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="21" t="inlineStr">
+        <is>
+          <t>「終わったよ」読書感想文をやり遂げた小6長男の、少し自信に満ちた顔</t>
+        </is>
+      </c>
+      <c r="C153" s="21" t="n"/>
+      <c r="D153" s="22" t="inlineStr">
+        <is>
+          <t>2029/02/24</t>
+        </is>
+      </c>
+      <c r="E153" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t>夏休みが終わりました🎒
+そして長男の読書感想文は…
+前日に無事終了しました！
+「今日やる」と言って何もしない日を1週間、
+残り2日でようやくエンジンがかかった長男。
+ぎりぎりでしたが書き上げました。
+過程は問いません。
+やり遂げたということで100点です💯
+「終わったよ」と報告してくれた表情は
+晴れやかで、少し自信に満ちた顔。
+…まぁ「ようやく解放された」のほうが
+大きい気もしますけどね😂
+文章を書くって本当に難しい。
+頭の中の思いを相手に分かるように文字にするのは
+大人でも苦労するところです。
+自分の思いや気づきを文章にすること。
+その入り口に少しは立てたのかな。
+今日から新学期です✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #読書感想文 #夏休みの宿題 #新学期 #小学6年生 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="154" ht="15.75" customHeight="1" s="18"/>
     <row r="155" ht="15.75" customHeight="1" s="18"/>
     <row r="156" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6815,6 +6815,14 @@
 晴れやかで、少し自信に満ちた顔。
 …まぁ「ようやく解放された」のほうが
 大きい気もしますけどね😂
+そしてもう一つ収穫が。
+本に出てきた「男尊女卑」という言葉を
+一緒に調べ、感想を言い合いました📚
+子どもに説明しようとすると
+自分の理解が曖昧なところが浮き彫りに。
+付き合ったつもりが私も勉強させてもらいました。
+宿題のサポートというより
+一緒に学んだ数日でした✨
 文章を書くって本当に難しい。
 頭の中の思いを相手に分かるように文字にするのは
 大人でも苦労するところです。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6816,7 +6816,8 @@
 …まぁ「ようやく解放された」のほうが
 大きい気もしますけどね😂
 そしてもう一つ収穫が。
-本に出てきた「男尊女卑」という言葉を
+長男が選んだ『キミの一歩　アフリカ』。
+そこに出てきた「男尊女卑」という言葉を
 一緒に調べ、感想を言い合いました📚
 子どもに説明しようとすると
 自分の理解が曖昧なところが浮き彫りに。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6790,7 +6790,11 @@
           <t>「終わったよ」読書感想文をやり遂げた小6長男の、少し自信に満ちた顔</t>
         </is>
       </c>
-      <c r="C153" s="21" t="n"/>
+      <c r="C153" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
       <c r="D153" s="22" t="inlineStr">
         <is>
           <t>2029/02/24</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6820,14 +6820,23 @@
 …まぁ「ようやく解放された」のほうが
 大きい気もしますけどね😂
 そしてもう一つ収穫が。
-長男が選んだ『キミの一歩　アフリカ』。
-そこに出てきた「男尊女卑」という言葉を
+長男が選んだのは『キミの一歩　アフリカ』。
+読み進めるうちに、こう言い出しました。
+「日本も男女平等って言われているけど、
+今の総理大臣は初めての女性総理だから、
+日本も昔はアフリカみたいに
+男尊女卑って感じだったんだろうね」
+…男尊女卑。小6の口から😳
+本で読んだアフリカと日本のニュースを
+自分の中で結びつけていたんです。
+面白くなってきたので、アフリカの背景を
 一緒に調べ、感想を言い合いました📚
 子どもに説明しようとすると
 自分の理解が曖昧なところが浮き彫りに。
-付き合ったつもりが私も勉強させてもらいました。
-宿題のサポートというより
-一緒に学んだ数日でした✨
+私も勉強させてもらいました。
+読書感想文ってこういうことなんだな。
+長男はちゃんと一番大事な部分をやっていた。
+書き出せなかっただけで✨
 文章を書くって本当に難しい。
 頭の中の思いを相手に分かるように文字にするのは
 大人でも苦労するところです。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -4385,7 +4385,7 @@
       </c>
       <c r="C99" s="19" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/08/27</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6849,7 +6849,56 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="15.75" customHeight="1" s="18"/>
+    <row r="154" ht="15.75" customHeight="1" s="18">
+      <c r="A154" s="23" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="23" t="inlineStr">
+        <is>
+          <t>「キツく言われるのはやだ」宿題で泣いた小1次男と、2人で決めたルール</t>
+        </is>
+      </c>
+      <c r="C154" s="23" t="n"/>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>2029/03/03</t>
+        </is>
+      </c>
+      <c r="E154" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F154" s="23" t="inlineStr">
+        <is>
+          <t>次男(小1)の宿題がうまく進まず、
+指摘すると喚いて、泣く😢
+最初は「またか」と思ったのですが
+落ち着いてから聞いてみたら違いました。
+泣いていた理由は
+「できないことが悔しかった」。
+「やりたくない」ではなく
+「できない自分が悔しい」。
+まったく別のことでした。
+嫌なことを聞き出すと2つ出てきました。
+・キツく言われるのはやだ
+・YouTubeやゲームを中断されるのはやだ
+そこで2人で決めたルール📝
+「YouTubeやゲームをやる前に、
+宿題と明日の支度ができているか一緒に確認する」
+順番を入れ替えただけ。
+でもこれなら楽しい時間が中断されません。
+私の約束も決めました。
+大きな声を出さない／優しい声かけ／叱らない
+やることを見える形にして、すぐ取りかかれる準備を。
+意志ではなく、順番で解決する。
+しばらくやってみます✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #宿題 #声かけ #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="155" ht="15.75" customHeight="1" s="18"/>
     <row r="156" ht="15.75" customHeight="1" s="18"/>
     <row r="157" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6858,7 +6858,11 @@
           <t>「キツく言われるのはやだ」宿題で泣いた小1次男と、2人で決めたルール</t>
         </is>
       </c>
-      <c r="C154" s="23" t="n"/>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
       <c r="D154" s="22" t="inlineStr">
         <is>
           <t>2029/03/03</t>
@@ -6891,6 +6895,11 @@
 私の約束も決めました。
 大きな声を出さない／優しい声かけ／叱らない
 やることを見える形にして、すぐ取りかかれる準備を。
+そして最後はハグ🤗
+「お互いに努力しようね」と励まし合いました。
+「あなたが直すこと」だけじゃなく
+私も直すことを決めた話し合い。
+だから「お互いに」なんです。
 意志ではなく、順番で解決する。
 しばらくやってみます✨
 ▶️ 続きはプロフィールのブログへ！

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6908,7 +6908,56 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="15.75" customHeight="1" s="18"/>
+    <row r="155" ht="15.75" customHeight="1" s="18">
+      <c r="A155" s="21" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>介護保険が使えない時期がいちばん大変。訪問看護師が伝えたい4つの選択肢</t>
+        </is>
+      </c>
+      <c r="C155" s="21" t="n"/>
+      <c r="D155" s="22" t="inlineStr">
+        <is>
+          <t>2029/03/10</t>
+        </is>
+      </c>
+      <c r="E155" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F155" s="21" t="inlineStr">
+        <is>
+          <t>親の通院に毎回付き添う。
+薬を取りに行くために早退する。
+「介護」というほどではない。
+でも一人で受診させるのは不安がある。
+介護保険を申請しても非該当。
+賄えないのに、手はかかる。
+そして担う家族の多くは仕事を持っています。
+支援の手がいちばん届いていない時期だと
+訪問看護師として感じています。
+でも、選択肢は4つあります✍️
+①訪問診療に切り替える(通院が不要になる)
+②訪問薬剤指導(薬を届けてもらえる)
+③家族会の支援(受診付き添い・電話相談)
+④自費の付き添いサービス
+①②は医療保険の話なので
+介護保険の認定がなくても使えます。
+ただし訪問診療にすると
+レントゲンなどの検査はしにくくなります。
+どこまで検査したいかは本人と家族の希望次第。
+そして入り口はすべて「主治医への相談」です。
+「通院が難しくなってきました」
+この一言から始まります。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#訪問看護 #親の介護 #介護保険 #通院付き添い #ワーママ #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="156" ht="15.75" customHeight="1" s="18"/>
     <row r="157" ht="15.75" customHeight="1" s="18"/>
     <row r="158" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6917,7 +6917,11 @@
           <t>介護保険が使えない時期がいちばん大変。訪問看護師が伝えたい4つの選択肢</t>
         </is>
       </c>
-      <c r="C155" s="21" t="n"/>
+      <c r="C155" s="21" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
       <c r="D155" s="22" t="inlineStr">
         <is>
           <t>2029/03/10</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6962,7 +6962,59 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="15.75" customHeight="1" s="18"/>
+    <row r="156" ht="15.75" customHeight="1" s="18">
+      <c r="A156" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="23" t="inlineStr">
+        <is>
+          <t>「クルトガダイブ」を手にした12歳の顔。3か月の約束を果たした長男の誕生日</t>
+        </is>
+      </c>
+      <c r="C156" s="23" t="n"/>
+      <c r="D156" s="22" t="inlineStr">
+        <is>
+          <t>2029/03/17</t>
+        </is>
+      </c>
+      <c r="E156" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F156" s="23" t="inlineStr">
+        <is>
+          <t>長男が12歳になりました🎂
+私も母になって12年。感慨深いです。
+プレゼントは念願の「クルトガダイブ」。
+入手困難と言われるシャープペンシルです✏️
+実はこれ、5月からの約束でした。
+パパが出した条件は
+「言われる前に自分で気づいて行動できるように
+なったら、8月末の誕生日にプレゼント」
+3か月、覚えていたと思います。
+夏休みもお手伝いを頑張っていました。
+手にした瞬間の笑顔。
+キラキラした目でまじまじ眺めて…
+そして「460回書くと芯が出る」を
+検証したくなった長男。
+10画の漢字を46個書こうとして、諦めました😂
+【12歳の率直レビュー】
+使い勝手 → 最高
+書き心地 → S20のほうが上
+強み → ノックしなくても書ける
+正直か。
+今日は友達に
+「そんなお高いペンを買ってもらって」
+と羨ましがられたそうです。
+…3か月かけて手に入れたんですよ✨
+12歳、おめでとう。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #誕生日 #クルトガダイブ #文房具好き #12歳 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="157" ht="15.75" customHeight="1" s="18"/>
     <row r="158" ht="15.75" customHeight="1" s="18"/>
     <row r="159" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7015,7 +7015,58 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="15.75" customHeight="1" s="18"/>
+    <row r="157" ht="15.75" customHeight="1" s="18">
+      <c r="A157" s="21" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="21" t="inlineStr">
+        <is>
+          <t>「欲しいものを買ってもらえる経験を買う」8000円のスクイーズを前に夫婦で話したこと</t>
+        </is>
+      </c>
+      <c r="C157" s="21" t="n"/>
+      <c r="D157" s="22" t="inlineStr">
+        <is>
+          <t>2029/03/24</t>
+        </is>
+      </c>
+      <c r="E157" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F157" s="21" t="inlineStr">
+        <is>
+          <t>次は長女の誕生日🎂
+欲しいのは今流行りの「スクイーズ」。
+本命は「メロジョイ」というもの。
+調べてみたら…プレミア価格で8000円近い😳
+一緒にAmazonで眺めていたら
+メロジョイ以外でも「これがいい！！」と
+テンションが上がったものがあったので
+私からのプレゼントはそれにしました。
+でも引っかかりが。
+一時的な流行りにこんな高いものを
+買っていいのだろうか。
+夫と話して出した答えは——
+「物を買うけれど、長女にとっては
+　欲しいものを買ってもらえる経験を買う」
+スクイーズはいつか飽きるでしょう。
+でも「欲しいと言ったものを
+ちゃんと聞いてもらえた」記憶は残る。
+物の値段で測ると高い買い物。
+経験の値段だと思えば、見え方が変わりました。
+とはいえ誕生日まではまだ日があります。
+小4の「これがいい！！」は
+1週間後には変わっていることも😂
+もう少し待ってみます。
+これから長女と話し合う過程も残していきます✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #誕生日プレゼント #スクイーズ #小学4年生 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="158" ht="15.75" customHeight="1" s="18"/>
     <row r="159" ht="15.75" customHeight="1" s="18"/>
     <row r="160" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -6971,7 +6971,11 @@
           <t>「クルトガダイブ」を手にした12歳の顔。3か月の約束を果たした長男の誕生日</t>
         </is>
       </c>
-      <c r="C156" s="23" t="n"/>
+      <c r="C156" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
       <c r="D156" s="22" t="inlineStr">
         <is>
           <t>2029/03/17</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7028,7 +7028,11 @@
           <t>「欲しいものを買ってもらえる経験を買う」8000円のスクイーズを前に夫婦で話したこと</t>
         </is>
       </c>
-      <c r="C157" s="21" t="n"/>
+      <c r="C157" s="21" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
       <c r="D157" s="22" t="inlineStr">
         <is>
           <t>2029/03/24</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7075,7 +7075,57 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="15.75" customHeight="1" s="18"/>
+    <row r="158" ht="15.75" customHeight="1" s="18">
+      <c r="A158" s="23" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="23" t="inlineStr">
+        <is>
+          <t>「これは帰ってきてからやりたい」小1次男に朝の勉強を提案して、1日で却下された話</t>
+        </is>
+      </c>
+      <c r="C158" s="23" t="n"/>
+      <c r="D158" s="22" t="inlineStr">
+        <is>
+          <t>2029/03/31</t>
+        </is>
+      </c>
+      <c r="E158" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F158" s="23" t="inlineStr">
+        <is>
+          <t>次男(小1)と毎晩数分の音読を続けています📖
+好きな本の読み聞かせも。
+短歌や俳句は言い回しに慣れず一言読み。
+でも何度か繰り返すと
+スムーズに読めるときも増えてきました。
+困るのは習い事のある日。
+宿題もあると音読の時間が取れません。
+そこで昨日、朝にやってみました。
+感触は悪くなかったのですが——
+今日、本人から申し出が。
+「これは帰ってきてからやりたい」
+なぜ朝にしたのか理由も一緒に確認して、
+そのうえで本人は「帰ってきてから頑張る」と。
+というわけで朝の試みは1日で中止です😂
+でも、いいと思っています。
+本人が「こうしたい」と言えたことのほうが
+朝にやるか夜にやるかより大事な気がして。
+自分で決めたなら、続く可能性が上がります。
+正直、手探りです。
+上の子では苦労しなかったので
+同じやり方が通用しないことに戸惑いも。
+担任の先生にも相談しながら探っています。
+同じように手探りの方、たくさんいますよね。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #音読 #家庭学習 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="159" ht="15.75" customHeight="1" s="18"/>
     <row r="160" ht="15.75" customHeight="1" s="18"/>
     <row r="161" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7081,7 +7081,7 @@
       </c>
       <c r="B158" s="23" t="inlineStr">
         <is>
-          <t>「これは帰ってきてからやりたい」小1次男に朝の勉強を提案して、1日で却下された話</t>
+          <t>「7時43分にやる」小1次男が自分で決めた時刻と、落花生ひと粒のパワーチャージ</t>
         </is>
       </c>
       <c r="C158" s="23" t="n"/>
@@ -7097,32 +7097,40 @@
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>次男(小1)と毎晩数分の音読を続けています📖
-好きな本の読み聞かせも。
-短歌や俳句は言い回しに慣れず一言読み。
-でも何度か繰り返すと
-スムーズに読めるときも増えてきました。
-困るのは習い事のある日。
-宿題もあると音読の時間が取れません。
-そこで昨日、朝にやってみました。
-感触は悪くなかったのですが——
-今日、本人から申し出が。
+          <t>次男(小1)と毎晩の音読と計算カード📖
+習い事のある日は時間が取れないので
+朝にやってみたら、翌日に本人から却下。
 「これは帰ってきてからやりたい」
-なぜ朝にしたのか理由も一緒に確認して、
-そのうえで本人は「帰ってきてから頑張る」と。
-というわけで朝の試みは1日で中止です😂
-でも、いいと思っています。
-本人が「こうしたい」と言えたことのほうが
-朝にやるか夜にやるかより大事な気がして。
-自分で決めたなら、続く可能性が上がります。
-正直、手探りです。
-上の子では苦労しなかったので
-同じやり方が通用しないことに戸惑いも。
-担任の先生にも相談しながら探っています。
-同じように手探りの方、たくさんいますよね。
+そして今日。案の定でした。
+やる気のない態度。
+「お母さんの言い方がきつい」
+放っておいてもうつ伏せのまま。
+そこで聞きました。
+「何時にやるの？　自分で決めて」
+返ってきた答えが——
+「7時43分」
+…43分。
+なぜその時刻？
+しかも寝る時間は8時。残り17分です😂
+でも本人が決めたこと。
+「わかりました」とアレクサでアラーム⏰
+7時43分。やる気のない様子は変わらず。
+決めたのは自分なのですが。
+そこに現れた助っ人が、ゆでた落花生。
+釣られて出てきた次男にひと粒。
+「パワーチャージです」
+…ようやく取り組んでくれました🥜
+5500円のシャープペンで動く長男もいれば
+落花生ひと粒で動く次男もいる。我が家です。
+時間はかかったけど寝る時間までに完了。
+めいっぱい褒め称えました✨
+正直、気が短い私にとって
+次男の計算カードは苦行でしかありません。
+でも今日はできました。
+明日も頑張ろう、私。笑
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
-#3人育児 #小学生ママ #小学1年生 #音読 #家庭学習 #子育て日記 #ドタバタ母さん</t>
+#3人育児 #小学生ママ #小学1年生 #家庭学習 #計算カード #子育て日記 #ドタバタ母さん</t>
         </is>
       </c>
     </row>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7134,7 +7134,72 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="15.75" customHeight="1" s="18"/>
+    <row r="159" ht="15.75" customHeight="1" s="18">
+      <c r="A159" s="21" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="21" t="inlineStr">
+        <is>
+          <t>「知らなかった、教えてくれてありがとう」宿題から逃げる小1次男の隣で、私も本を開いた日</t>
+        </is>
+      </c>
+      <c r="C159" s="21" t="n"/>
+      <c r="D159" s="22" t="inlineStr">
+        <is>
+          <t>2029/04/07</t>
+        </is>
+      </c>
+      <c r="E159" s="21" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F159" s="21" t="inlineStr">
+        <is>
+          <t>我が家のルール📖
+宿題と明日の支度が済んでから
+好きな時間(ゲームやYouTube)を獲得できる。
+長男も長女もこれで育ってきました。
+今朝、そのルールを確認しようとしたら
+次男は聞く耳持たず。
+「お話すら聞けないのであれば
+　ゲームやYouTubeを見る資格はありません」
+思い切ってデジタルデトックス開始です。
+帰宅すると、ランドセルは散乱。宿題も手つかず。
+そして長女のゲームを後ろから眺めて笑っている次男😇
+まずは片付けから声かけ → 意外にもスムーズ。
+「宿題いつやるの？」→「お風呂入ってから」
+そしてダラダラし始めたので
+「お風呂入ってからやると決めたのは自分。
+　自分との約束は守りましょう」
+兄弟には別室に移動してもらい、静かな環境に。
+すると次男が
+「お母さん、知ってる？」
+と関係ない話を次々と…！
+以前なら「今は宿題の時間でしょう」と
+言っていたと思います。
+でも今日はこう返しました。
+「知らなかった、教えてくれてありがとう」
+そして私も自分の本を出して勉強を始めました📚
+しばらくすると——次男が集中し始めたんです。
+漢字、プリント、音読、計算カードまで
+ぐずぐずせずにやり切りました✨
+計算カードは2分52秒。目標の2分より遅く
+本人は残念そう。
+でも私が伝えたのは別のこと。
+取り組むまでの速さ、集中、真剣さ、
+最後まで丁寧にやり切ったこと。
+すごく成長しているよ、とハイタッチ🙌
+デジタルデトックスが良かったのか
+私がガミガミ言わなかったからか
+正直わかりません。
+でも今日は、苦行ではなかったです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #宿題 #デジタルデトックス #声かけ #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="160" ht="15.75" customHeight="1" s="18"/>
     <row r="161" ht="15.75" customHeight="1" s="18"/>
     <row r="162" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7190,6 +7190,18 @@
 取り組むまでの速さ、集中、真剣さ、
 最後まで丁寧にやり切ったこと。
 すごく成長しているよ、とハイタッチ🙌
+そして今日、整理がついたこと。
+過干渉になってもうざいと思われるだけ。
+一歩俯瞰して、事実を確認したり
+一緒に勉強する時間にしたほうが
+よっぽど自分のためにもいい。
+我が家で口うるさく言うのはこの3つだけ。
+・自分が怪我する/他人に怪我をさせる危険な行動
+・日々の生活リズム
+・我が家のルール
+それ以外は「余白」も大事。
+あまり干渉しないほうが
+子どもも自分で考えて行動するのかもしれません🌱
 デジタルデトックスが良かったのか
 私がガミガミ言わなかったからか
 正直わかりません。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7212,7 +7212,60 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="15.75" customHeight="1" s="18"/>
+    <row r="160" ht="15.75" customHeight="1" s="18">
+      <c r="A160" s="23" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="23" t="inlineStr">
+        <is>
+          <t>明日はピアノの発表会。次男が今朝から弾き始めた曲が、まさかの本番曲でした</t>
+        </is>
+      </c>
+      <c r="C160" s="23" t="n"/>
+      <c r="D160" s="22" t="inlineStr">
+        <is>
+          <t>2029/04/14</t>
+        </is>
+      </c>
+      <c r="E160" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F160" s="23" t="inlineStr">
+        <is>
+          <t>明日は3人そろってピアノの発表会🎹
+1年間の頑張りを発表する場です。
+そんなわけで今日は最後のレッスン。
+【長女】
+「お風呂が沸きました」でおなじみのあの曲。
+楽しそうに弾けています。仕上がり順調✨
+【次男】
+今朝、急に「聖者の行進」を弾き始めました。
+なんだろうと思っていたら…
+この曲を発表会で弾くらしいと今日判明。
+今日。明日が本番です。
+大丈夫か、次男😂
+【長男】
+今日は特別レッスン。
+プロのピアニストの方に直接教えてもらえて
+明日の本番ではその方と連弾するのだそうです。
+なんだかすごいことのようですが
+当の本人は
+「珍しい経験だからちゃんと…」
+と言いながら携帯ゲームに夢中でした。
+緊張感、どこ🤔
+長女は仕上がり順調
+次男は今日曲を知ったばかり
+長男はプロと連弾
+三者三様すぎます。
+明日の発表会が楽しみです🎼
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #ピアノ #ピアノ発表会 #習い事 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="161" ht="15.75" customHeight="1" s="18"/>
     <row r="162" ht="15.75" customHeight="1" s="18"/>
     <row r="163" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7239,6 +7239,12 @@
 そんなわけで今日は最後のレッスン。
 【長女】
 「お風呂が沸きました」でおなじみのあの曲。
+曲名を聞いてみたら
+「人形の夢と…なんとか」
+…なんとか😂
+正しくは「人形の夢と目ざめ」です。
+でも確かに、なんとかの部分が
+思い出せない曲でもある。
 楽しそうに弾けています。仕上がり順調✨
 【次男】
 今朝、急に「聖者の行進」を弾き始めました。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7254,9 +7254,15 @@
 大丈夫か、次男😂
 【長男】
 今日は特別レッスン。
-プロのピアニストの方に直接教えてもらえて
-明日の本番ではその方と連弾するのだそうです。
-なんだかすごいことのようですが
+プロのピアニストの方に直接教えてもらえます。
+その道に詳しくないので調べて驚きました。
+・国際ピアノコンクールで第1位・グランプリ
+・国内の登竜門で最上位カテゴリのファイナリスト
+・音大の大学院で研鑽を積む現役の演奏家
+…とんでもない方でした😳
+そして明日の本番ではその方と連弾。
+小6がこんな機会をもらえることまずありません。
+なのに当の本人は
 当の本人は
 「珍しい経験だからちゃんと…」
 と言いながら携帯ゲームに夢中でした。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7218,10 +7218,14 @@
       </c>
       <c r="B160" s="23" t="inlineStr">
         <is>
-          <t>明日はピアノの発表会。次男が今朝から弾き始めた曲が、まさかの本番曲でした</t>
-        </is>
-      </c>
-      <c r="C160" s="23" t="n"/>
+          <t>今日はピアノの発表会。次男が昨日から弾き始めた曲が、まさかの本番曲でした</t>
+        </is>
+      </c>
+      <c r="C160" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
       <c r="D160" s="22" t="inlineStr">
         <is>
           <t>2029/04/14</t>
@@ -7234,9 +7238,9 @@
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>明日は3人そろってピアノの発表会🎹
+          <t>この日は3人そろってピアノの発表会🎹
 1年間の頑張りを発表する場です。
-そんなわけで今日は最後のレッスン。
+そんなわけで前日は最後のレッスン。
 【長女】
 「お風呂が沸きました」でおなじみのあの曲。
 曲名を聞いてみたら
@@ -7247,38 +7251,125 @@
 思い出せない曲でもある。
 楽しそうに弾けています。仕上がり順調✨
 【次男】
-今朝、急に「聖者の行進」を弾き始めました。
+発表会の前日の朝、急に「聖者の行進」を弾き始めました。
 なんだろうと思っていたら…
-この曲を発表会で弾くらしいと今日判明。
-今日。明日が本番です。
+この曲を発表会で弾くらしいと前日に判明。
+前日。翌日が本番です。
 大丈夫か、次男😂
 【長男】
-今日は特別レッスン。
+前日は特別レッスン。
 プロのピアニストの方に直接教えてもらえます。
 その道に詳しくないので調べて驚きました。
 ・国際ピアノコンクールで第1位・グランプリ
 ・国内の登竜門で最上位カテゴリのファイナリスト
 ・音大の大学院で研鑽を積む現役の演奏家
 …とんでもない方でした😳
-そして明日の本番ではその方と連弾。
+そして本番ではその方と連弾。
 小6がこんな機会をもらえることまずありません。
 なのに当の本人は
-当の本人は
 「珍しい経験だからちゃんと…」
 と言いながら携帯ゲームに夢中でした。
 緊張感、どこ🤔
 長女は仕上がり順調
-次男は今日曲を知ったばかり
+次男は前日に曲を知ったばかり
 長男はプロと連弾
 三者三様すぎます。
-明日の発表会が楽しみです🎼
+さあ、本番です🎼
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
 #3人育児 #小学生ママ #ピアノ #ピアノ発表会 #習い事 #子育て日記 #ドタバタ母さん</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="15.75" customHeight="1" s="18"/>
+    <row r="161" ht="15.75" customHeight="1" s="18">
+      <c r="A161" s="23" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="23" t="inlineStr">
+        <is>
+          <t>抱きかかえられて登場した次男、リベンジを申し出た長女。3人とも最後まで弾き切りました</t>
+        </is>
+      </c>
+      <c r="C161" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/06</t>
+        </is>
+      </c>
+      <c r="D161" s="22" t="inlineStr">
+        <is>
+          <t>2029/04/21</t>
+        </is>
+      </c>
+      <c r="E161" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F161" s="23" t="inlineStr">
+        <is>
+          <t>ピアノの発表会、無事に終わりました🎹
+【長男】
+まず「ビリーブ」をプロのピアニストの方の
+伴奏で歌いました。爽やかに歌えました✨
+そしてピアノのソロ。
+…途中で完全に調子が狂ったのが
+見ていて分かりました。
+そこからはつっかえ、つっかえ。
+でも、最後まで弾くことができました。
+一方「コウを追いかけて」の連弾は
+プロの方にセコンドをやっていただき
+素晴らしい演奏でした。
+支えてくれる人がいると
+こんなに違うのかと思いました。
+【次男】
+順番が近くなってくると
+「つまんないからピアノやりたくないなぁ」
+…嫌な予感😇
+そして直前に本格的にごね始め
+舞台袖からの入場は
+ピアノの先生に抱きかかえられる格好で登場。
+座っても弾こうとせず
+先生が先導して一緒になんとか
+「かっこう」と「聖者の行進」を。
+でも、ここからでした。
+演奏のあと、先生と何やらコソコソ話。
+どうやら気合を入れてもらったらしく——
+その後、一人で「聖者の行進」を
+弾き切ることができました👏
+たぶん直前の緊張で
+失敗を回避したかったのだと思います。
+逃げずに頑張りました。
+【長女】
+自宅ではすらすら弾けていた曲。
+でも本番の緊張もあったのでしょう
+譜面が飛んでしまい、最後まで弾けず。
+ここで終わらなかったのが長女でした。
+「リベンジしたい」
+本人の希望を通していただき
+もう一度発表させてもらえたのです。
+そして2回目。
+「2回目のほうが上手にできた」
+笑顔で舞台から降りてきました😊
+つっかえた長男。
+抱きかかえられて登場した次男。
+譜面が飛んだ長女。
+それでも3人とも、最後まで弾き切りました。
+この1年間の成果発表ではありますが
+毎朝ピアノに向き合い
+日々頑張ってきた努力は絶対に裏切りません。
+あの時の努力できた自分が
+苦難に立ったときの自分を
+励ましてくれると思うのです。
+今回の発表会は
+3人それぞれの自信になったのではないかと
+感じています。
+みんな頑張りました。お疲れさま🌸
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #ピアノ #ピアノ発表会 #習い事 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="162" ht="15.75" customHeight="1" s="18"/>
     <row r="163" ht="15.75" customHeight="1" s="18"/>
     <row r="164" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7223,7 +7223,7 @@
       </c>
       <c r="C160" s="23" t="inlineStr">
         <is>
-          <t>2026/09/06</t>
+          <t>2026/09/06T08:00:00+09:00</t>
         </is>
       </c>
       <c r="D160" s="22" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C161" s="23" t="inlineStr">
         <is>
-          <t>2026/09/06</t>
+          <t>2026/09/07T07:20:53+09:00</t>
         </is>
       </c>
       <c r="D161" s="22" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7084,7 +7084,11 @@
           <t>「7時43分にやる」小1次男が自分で決めた時刻と、落花生ひと粒のパワーチャージ</t>
         </is>
       </c>
-      <c r="C158" s="23" t="n"/>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/07T09:07:45+09:00</t>
+        </is>
+      </c>
       <c r="D158" s="22" t="inlineStr">
         <is>
           <t>2029/03/31</t>
@@ -7292,7 +7296,7 @@
       </c>
       <c r="C161" s="23" t="inlineStr">
         <is>
-          <t>2026/09/07T07:20:53+09:00</t>
+          <t>2026/09/06T18:00:00+09:00</t>
         </is>
       </c>
       <c r="D161" s="22" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7374,7 +7374,75 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="15.75" customHeight="1" s="18"/>
+    <row r="162" ht="15.75" customHeight="1" s="18">
+      <c r="A162" s="23" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="23" t="inlineStr">
+        <is>
+          <t>「傘忘れたでしょう！」弟に喝を入れた長女。よく気づいたね、と感動したのも束の間でした</t>
+        </is>
+      </c>
+      <c r="C162" s="23" t="n"/>
+      <c r="D162" s="22" t="inlineStr">
+        <is>
+          <t>2029/04/28</t>
+        </is>
+      </c>
+      <c r="E162" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F162" s="23" t="inlineStr">
+        <is>
+          <t>次男(小1)がスイミングに傘を忘れてきました☔️
+「傘、忘れてきた」
+帰りは雨が降っていなかったそうです。
+まあ、降ってなければ思い出さないですよね。
+でも明日も雨予報。
+予備の傘はあるけど
+忘れた傘は取りに行かないといけない。
+明日、スイミングに取りに行くか…
+正直ゲンナリしていました😩
+そして1時間後。
+我が家は次男の1時間後に長女(小4)が
+スイミングに行きます。
+長女が帰宅するや否や、開口一番。
+「傘忘れたでしょう！」
+次男に喝が入りました。
+…え。なんで知ってるの。
+私は本気で感動しました。
+自分のことで精一杯になりがちな小4が
+弟の忘れ物に気づいたなんて。
+しかもこちらが何も言っていないのに。
+長女、よく気づいた！すごい！すごい！！
+お姉ちゃんだなあとしみじみ😊
+あまりに感心したので聞いてみました。
+どうして次男が傘を忘れたって分かったの？
+長女の答えが——
+「傘忘れたー！って思って取りに戻ったら
+〇〇の傘があったから持って帰ってきたんだよ」
+……あなたも忘れてたんかーい😂
+一度帰ろうとして、途中で気づいて取りに戻り
+そこでたまたま弟の傘を見つけただけ。
+感動したあの数十秒を返してほしい。
+でも突っ込みたい気持ちはグッと抑えました。
+だって結果を見ると
+・傘は2本とも家にある
+・明日私が取りに行く必要はない
+・弟の忘れ物にも対応してくれた
+…完璧じゃないですか✨
+過程はどうあれ、やったことは立派。
+自分の傘を取りに戻る手間をかけて
+弟の傘まで持って帰ってきたんです。
+めいっぱい褒め称えた夜でした🌙
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学4年生 #小学1年生 #きょうだい #忘れ物 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="163" ht="15.75" customHeight="1" s="18"/>
     <row r="164" ht="15.75" customHeight="1" s="18"/>
     <row r="165" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7147,7 +7147,11 @@
           <t>「知らなかった、教えてくれてありがとう」宿題から逃げる小1次男の隣で、私も本を開いた日</t>
         </is>
       </c>
-      <c r="C159" s="21" t="n"/>
+      <c r="C159" s="21" t="inlineStr">
+        <is>
+          <t>2026/09/10T09:08:45+09:00</t>
+        </is>
+      </c>
       <c r="D159" s="22" t="inlineStr">
         <is>
           <t>2029/04/07</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7447,7 +7447,85 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="15.75" customHeight="1" s="18"/>
+    <row r="163" ht="15.75" customHeight="1" s="18">
+      <c r="A163" s="23" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="23" t="inlineStr">
+        <is>
+          <t>「5時に起こして」宿題が終わらなかった日、小1次男が自分で決めた翌朝</t>
+        </is>
+      </c>
+      <c r="C163" s="23" t="n"/>
+      <c r="D163" s="22" t="inlineStr">
+        <is>
+          <t>2029/05/05</t>
+        </is>
+      </c>
+      <c r="E163" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F163" s="23" t="inlineStr">
+        <is>
+          <t>次男(小1)の宿題、終わらなかった日の話📖
+その日はぐずぐず、ぐずぐず。
+音読とプリントはできましたが
+直しは手つかず。書き取りも計算カードも
+残ったまま20時になりました。
+我が家の次男は20時が寝る時間。
+そして20時からは
+寝る前の音読と好きな本を読む時間を
+一緒に過ごしています。
+「宿題終わってないから今日は本なし」
+以前の私ならそう言っていたと思います。
+でも、この時間は削りません。
+理由があります。
+続けてそろそろ1か月になるのですが
+最近はっきり感じることがあるんです。
+文章の読み方が変わってきました。
+始めたころは一言ずつ区切る読み方。
+それが今は、まとまりのある言葉で
+読めるようになってきている。
+しかも、それが早くなってきている。
+…音読、侮れないです✨
+そしてもうひとつ大事なこと。
+本人がこの時間を楽しみにしているんです。
+20時になると自然と本を持ってくる。
+ここを削ったら、1か月かけて
+積み上げたものが崩れる気がして。
+その日も本を読んで、就寝しました。
+宿題を残したままです。
+でも本人も気にしていて
+布団に入る前にこう言いました。
+「5時に起こして」
+…5時。
+翌朝、言われたとおり起こしました。
+正直「起きないだろうな」と思いながら。
+ところが——
+意外にもスッと起きたんです😳
+少しぼんやりしていましたが
+そのあとちゃんと机に向かい
+なんとか6時には終えることができました。
+計算カードの目標タイムには
+まだまだ届きません。
+でも私がよかったと思っているのは
+本人が決めたことをサポートできたこと。
+「5時に起こして」と言ったのは次男。
+私が決めたわけではありません。
+日によってやる気はまちまちです。
+明日はまたうつ伏せかもしれません😅
+でも一歩ずつ進んでいることは確かです。
+先導するのでも、見張るのでもなく
+隣を一緒に走るイメージで
+引き続き伴走していきます🌱
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #家庭学習 #音読 #宿題 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="164" ht="15.75" customHeight="1" s="18"/>
     <row r="165" ht="15.75" customHeight="1" s="18"/>
     <row r="166" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7526,7 +7526,73 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="15.75" customHeight="1" s="18"/>
+    <row r="164" ht="15.75" customHeight="1" s="18">
+      <c r="A164" s="23" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="23" t="inlineStr">
+        <is>
+          <t>アイスベストは入浴介助で雲泥の差。訪問看護師が1年使ってわかったこと</t>
+        </is>
+      </c>
+      <c r="C164" s="23" t="n"/>
+      <c r="D164" s="22" t="inlineStr">
+        <is>
+          <t>2029/05/12</t>
+        </is>
+      </c>
+      <c r="E164" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F164" s="23" t="inlineStr">
+        <is>
+          <t>今日は子どもの話ではなく、仕事の話です🩺
+訪問看護師として働いている私。
+夏の暑さ対策に、去年から職場で
+アイスベストを使っています。
+保冷剤をベストに入れて
+背中と脇の下を冷やすだけ。
+正直、たかが保冷剤と
+まったく期待していませんでした。
+でも一回着てみたら
+もう夏の訪問には欠かせません✨
+いちばん差が出るのは、入浴介助。
+蒸気あふれる浴室で
+着る・着ないは雲泥の差です。
+【1年使ってわかったメリット】
+・電源がいらない
+・午前中の訪問から戻っても保冷剤がまだ冷たい
+・メッシュで薄くて軽い
+・洗ってもすぐ乾く
+訪問看護は車だけじゃなく
+場所や天気によって自転車や徒歩の日も🚲
+移動中から冷やせるので
+吹き出す汗が減りました。
+浴室で使うなら空調服よりこっち。
+周りの空気が熱くて湿っているので
+ファンで取り込んでも涼しくなりにくいんです。
+【デメリット】
+保冷剤4つぶんの冷凍庫スペースが必要。
+【職場ではこう回しています】
+・ベスト3着をみんなで共有
+・保冷剤は12個
+・冷えているものから使う
+・昼に戻って冷凍庫へ → 午後にまた使える
+全員分じゃなくても回ります。
+職場に導入を考えている方の
+参考になればうれしいです。
+※アイスベストは暑さ対策のひとつ。
+こまめな水分補給や休憩とセットで🥤
+残暑はまだまだ続きそう。
+もうしばらくお世話になります。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#訪問看護 #訪問看護師 #看護師ママ #入浴介助 #暑さ対策 #熱中症対策 #アイスベスト #ワーキングマザー #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="165" ht="15.75" customHeight="1" s="18"/>
     <row r="166" ht="15.75" customHeight="1" s="18"/>
     <row r="167" ht="15.75" customHeight="1" s="18"/>
